--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
@@ -44,7 +44,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'OPS·品質維運'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'技術流程對照'!$A$4:$L$69</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'技術流程對照'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'元件標籤字典'!$A$4:$H$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'元件標籤字典'!$A$4:$I$105</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'元件標籤字典'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -740,7 +740,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>agent → api X-Internal-Token（api 側驗證失敗即拒絕、常數時間比對）；品牌 api → OHS 採 Casdoor OIDC OAuth 2.0 client_credentials，JWT 必驗 issuer/audience/expiry，無效或過期憑證 100% 回 401</t>
+          <t>agent → api X-Internal-Token（api 側驗證失敗即拒絕、常數時間比對）；品牌 api → OHS 服務憑證（機制 [待確認]）</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>驗證方式：正常、錯 issuer、錯 audience、過期、撤銷五類整合測試</t>
+          <t>驗證方式：整合測試上游含 [待確認]，需先定量測環境/關卡。</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>✅ 營運目標</t>
+          <t>❓ 待確認</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>上線候選內容 100% 經人工審核；每版不足 100 筆時全驗，否則至少抽驗 100 筆且不低於該版 10%；一般內容誤放率 ≤ 1%，高風險內容誤放 1 筆即阻擋發布</t>
+          <t>人工審核為品質防線；核可通過率 / 抽樣誤放率門檻 [待確認]</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>驗證方式：依風險分層抽樣人工審核 + 發布 gate 報表</t>
+          <t>驗證方式：抽樣人工審核上游含 [待確認]，需先定量測環境/關卡。</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>✅ 營運目標</t>
+          <t>❓ 待確認</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>原始資產 100% 原樣落 raw object storage，保存 content hash、source URI、acquired_at；至少保留 1 年或至衍生 bronze 退役（取較長者）</t>
+          <t>原始資產保存策略 [待確認]</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>驗證方式：每季按來源類型抽 10 筆從 raw 重建 bronze，hash/provenance 100% 一致</t>
+          <t>驗證方式：保存位置文件化上游含 [待確認]，需先定量測環境/關卡。</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>✅ 營運目標</t>
+          <t>❓ 待確認</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>每個 RC 以 Playwright 100% 涵蓋九條關鍵流：LINE 建案、報價同意、付款、派工 SLA、技師接拒單/到場/requote、結算退款、跨租戶拒絕、知識人工審核發布、租戶開站/License</t>
+          <t>Playwright 涵蓋關鍵營運流程（範圍 [待確認]）</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>驗證方式：E2E CI；任一關鍵流失敗即阻擋 RC</t>
+          <t>驗證方式：E2E CI 上游含 [待確認]，需先定量測環境/關卡。</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>✅ 營運目標</t>
+          <t>❓ 待確認</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
@@ -6414,17 +6414,17 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>line_gateway; AgentLoop; AgentRunner</t>
+          <t>line_gateway; Photo Guide resolver; Quote postback message mapper; WebhookIdempotencyStore; AgentLoop; AgentRunner</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L138–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
@@ -6476,17 +6476,17 @@
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>line_gateway; AgentLoop; AgentRunner</t>
+          <t>line_gateway; Photo Guide resolver; Quote postback message mapper; WebhookIdempotencyStore; AgentLoop; AgentRunner</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L138–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
@@ -6538,17 +6538,17 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
@@ -6600,17 +6600,17 @@
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="L8" s="13" t="inlineStr">
@@ -6662,17 +6662,17 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
@@ -6724,17 +6724,17 @@
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; 記憶 DB</t>
+          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; SkillSync; 記憶 DB</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
+          <t>15_SDS §5.1</t>
         </is>
       </c>
       <c r="L10" s="13" t="inlineStr">
@@ -6786,17 +6786,17 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; 記憶 DB</t>
+          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; SkillSync; 記憶 DB</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
+          <t>15_SDS §5.1</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L369–374; §5.4</t>
+          <t>15_SDS §5.1、§5.4</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr">
@@ -6910,17 +6910,17 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
@@ -6972,17 +6972,17 @@
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>line_gateway; AgentLoop; AgentRunner</t>
+          <t>line_gateway; Photo Guide resolver; Quote postback message mapper; WebhookIdempotencyStore; AgentLoop; AgentRunner</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L138–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L369–374; §5.4</t>
+          <t>15_SDS §5.1、§5.4</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
@@ -7096,17 +7096,17 @@
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
       <c r="L16" s="13" t="inlineStr">
@@ -7158,17 +7158,17 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
       <c r="L17" s="11" t="inlineStr">
@@ -7220,17 +7220,17 @@
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
       <c r="L18" s="13" t="inlineStr">
@@ -7282,17 +7282,17 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）; Flow DSL executor; domain blocks / primitives; core/db.py</t>
+          <t>Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; core/db.py</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
       <c r="L19" s="11" t="inlineStr">
@@ -7344,17 +7344,17 @@
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）; Redis pub/sub; Kafka; 分散式排程</t>
+          <t>Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="L20" s="13" t="inlineStr">
@@ -7406,17 +7406,17 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）; Redis pub/sub; Kafka; 分散式排程</t>
+          <t>Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
@@ -7468,17 +7468,17 @@
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）; Redis pub/sub; Kafka; 分散式排程</t>
+          <t>Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
       <c r="L22" s="13" t="inlineStr">
@@ -7530,17 +7530,17 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）; Flow DSL executor; domain blocks / primitives; core/db.py</t>
+          <t>Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; core/db.py</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
       <c r="L23" s="11" t="inlineStr">
@@ -7592,17 +7592,17 @@
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）; Flow DSL executor; domain blocks / primitives; core/db.py</t>
+          <t>Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; core/db.py</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
       <c r="L24" s="13" t="inlineStr">
@@ -7659,12 +7659,12 @@
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
       <c r="L25" s="11" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
       <c r="L26" s="13" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
       <c r="L27" s="11" t="inlineStr">
@@ -7840,17 +7840,17 @@
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; Kafka; line_push_service + outbox worker</t>
+          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; EventBusProducer; Kafka; line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
       <c r="L28" s="13" t="inlineStr">
@@ -7902,17 +7902,17 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; Kafka; line_push_service + outbox worker</t>
+          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; EventBusProducer; Kafka; line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
       <c r="L29" s="11" t="inlineStr">
@@ -7964,17 +7964,17 @@
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; Kafka; line_push_service + outbox worker</t>
+          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; EventBusProducer; Kafka; line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -8026,17 +8026,17 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="L31" s="11" t="inlineStr">
@@ -8088,17 +8088,17 @@
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
@@ -8150,17 +8150,17 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
       <c r="L33" s="11" t="inlineStr">
@@ -8212,17 +8212,17 @@
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
       <c r="L36" s="13" t="inlineStr">
@@ -8398,17 +8398,17 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="L37" s="11" t="inlineStr">
@@ -8460,17 +8460,17 @@
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="L38" s="13" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L570–578</t>
+          <t>15_SDS §8.1</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
@@ -8584,17 +8584,17 @@
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
       <c r="L41" s="11" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.6 L199–208</t>
+          <t>12_SAD §4.6</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L611–613; 附錄 L736</t>
+          <t>15_SDS §9.1；附錄</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
@@ -8770,17 +8770,17 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; forward-only migrations; platform schema; core/db.py</t>
+          <t>SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
       <c r="L43" s="11" t="inlineStr">
@@ -8832,17 +8832,17 @@
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; forward-only migrations; platform schema; core/db.py</t>
+          <t>SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §8.1 L353–361; §9 L407</t>
+          <t>12_SAD §5、§8–9</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677</t>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
         </is>
       </c>
       <c r="L45" s="11" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L179–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L614–615; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
@@ -9204,17 +9204,17 @@
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>Draft Queue; 審核 UI backend</t>
+          <t>Draft Queue; 審核 UI backend; Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L615–616; §9.2 L621–629</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Publisher; 品牌庫 pgvector; SkillsLoader + 2 builtin skills</t>
+          <t>Publisher; behavior patch artifact; LiveSkill DB ingest; 品牌庫 pgvector; SkillsLoader + 2 builtin skills</t>
         </is>
       </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L617–619; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>Draft Queue; 審核 UI backend</t>
+          <t>Draft Queue; 審核 UI backend; Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="J52" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L615–616; §9.2 L621–629</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -9390,17 +9390,17 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>self-service routers; 守衛鏈; technician_service; certification/kyc_service; lock_tech</t>
+          <t>API_SURFACE router filter; self-service routers; 守衛鏈; technician_service; certification/kyc_service; Tech DB router + mirror; lock_tech</t>
         </is>
       </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="L53" s="11" t="inlineStr">
@@ -9452,17 +9452,17 @@
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>self-service routers; 守衛鏈; technician_service; certification/kyc_service; lock_tech</t>
+          <t>API_SURFACE router filter; self-service routers; 守衛鏈; technician_service; certification/kyc_service; Tech DB router + mirror; lock_tech</t>
         </is>
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K54" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -9514,17 +9514,17 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>OHS API routers; matching_service; schedule_service; WebSocket 端點; 事件層</t>
+          <t>OHS API routers; dispatch_service candidate scoring; schedule_service; WebSocket 端點; 事件層</t>
         </is>
       </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
       <c r="L55" s="11" t="inlineStr">
@@ -9576,17 +9576,17 @@
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>OHS API routers; matching_service; schedule_service; WebSocket 端點; 事件層</t>
+          <t>OHS API routers; dispatch_service candidate scoring; schedule_service; WebSocket 端點; 事件層</t>
         </is>
       </c>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K56" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -9638,17 +9638,17 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>事件層; 技師工單 read-model; WebSocket 端點</t>
+          <t>事件層; EventConsumerWorker; technician_workorder_projection; 技師工單 read-model; WebSocket 端點</t>
         </is>
       </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="L57" s="11" t="inlineStr">
@@ -9700,17 +9700,17 @@
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
-          <t>commission_settlement_service; 技師工單 read-model; Kafka</t>
+          <t>technician settlement services; technician_commission_projection; EventConsumerWorker; Kafka</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197; §9 L401</t>
+          <t>12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="K58" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
@@ -9762,17 +9762,17 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>OHS API routers; matching_service; schedule_service; WebSocket 端點; 事件層</t>
+          <t>OHS API routers; dispatch_service candidate scoring; schedule_service; WebSocket 端點; 事件層</t>
         </is>
       </c>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
       <c r="L59" s="11" t="inlineStr">
@@ -9824,17 +9824,17 @@
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>self-service routers; 守衛鏈; technician_service; certification/kyc_service; lock_tech</t>
+          <t>API_SURFACE router filter; self-service routers; 守衛鏈; technician_service; certification/kyc_service; Tech DB router + mirror; lock_tech</t>
         </is>
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="K60" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
@@ -9886,17 +9886,17 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>Casdoor; 平台維運 console; 守衛鏈; License provisioning</t>
+          <t>Casdoor; 平台維運 console; 守衛鏈; License Entitlement Gate; License provisioning</t>
         </is>
       </c>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="L61" s="11" t="inlineStr">
@@ -9948,17 +9948,17 @@
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>Casdoor; 平台維運 console; 守衛鏈; License provisioning</t>
+          <t>Casdoor; 平台維運 console; 守衛鏈; License Entitlement Gate; License provisioning</t>
         </is>
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="K62" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>Casdoor; 平台維運 console; 守衛鏈; License provisioning</t>
+          <t>Casdoor; 平台維運 console; 守衛鏈; License Entitlement Gate; License provisioning</t>
         </is>
       </c>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="K63" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
       <c r="L63" s="11" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394</t>
+          <t>12_SAD §4.2、§8–9</t>
         </is>
       </c>
       <c r="K64" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677</t>
+          <t>15_SDS §6.1、§6.3、§11</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L146; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.2 L68; §5.1 L370; §13 L707</t>
+          <t>15_SDS §2.2、§5.1、§13</t>
         </is>
       </c>
       <c r="L65" s="11" t="inlineStr">
@@ -10196,17 +10196,17 @@
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>SigNoz; OPIK; OpenTelemetry</t>
+          <t>SigNoz; OPIK; OpenTelemetry; PIIScrubSpanProcessor</t>
         </is>
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>12_SAD §8.2、§9</t>
         </is>
       </c>
       <c r="K66" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
+          <t>15_SDS §12</t>
         </is>
       </c>
       <c r="L66" s="13" t="inlineStr">
@@ -10263,12 +10263,12 @@
       </c>
       <c r="J67" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396–398</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="K67" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644</t>
+          <t>15_SDS §2.1、§3.2–3.7、§10</t>
         </is>
       </c>
       <c r="L67" s="11" t="inlineStr">
@@ -10320,17 +10320,17 @@
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry; Vertical Pack; HITL 審核骨架</t>
+          <t>Agent Configuration Studio / Config Registry; M18 Config Registry; Skill Revision Registry; Vertical Pack; HITL 審核骨架</t>
         </is>
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396, L398, L400</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="K68" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
+          <t>15_SDS §3.2、§10、§13</t>
         </is>
       </c>
       <c r="L68" s="13" t="inlineStr">
@@ -10382,17 +10382,17 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry; Vertical Pack; HITL 審核骨架</t>
+          <t>Agent Configuration Studio / Config Registry; M18 Config Registry; Skill Revision Registry; Vertical Pack; HITL 審核骨架</t>
         </is>
       </c>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396, L398, L400</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="K69" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
+          <t>15_SDS §3.2、§10、§13</t>
         </is>
       </c>
       <c r="L69" s="11" t="inlineStr">
@@ -10561,7 +10561,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10569,9 +10569,10 @@
     <col width="72" customWidth="1" min="3" max="3"/>
     <col width="68" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="58" customWidth="1" min="7" max="7"/>
-    <col width="80" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -10616,17 +10617,22 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
+          <t>Code reality</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
           <t>SAD 定位</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>SDS 定位</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>能力群相關實作路徑 / 規劃狀態</t>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>實作證據路徑</t>
         </is>
       </c>
     </row>
@@ -10643,7 +10649,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>LINE 通道閘道：接收 webhook、驗證 X-Line-Signature、分派訊息/事件，並將回覆送回 LINE。</t>
+          <t>LINE 通道閘道：接收 webhook、驗證 X-Line-Signature、分派文字/照片/postback，並將文字與核准圖片回覆送回 LINE。</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -10656,17 +10662,22 @@
           <t>AGT·CHN</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L138–149</t>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
@@ -10675,217 +10686,242 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>AgentLoop</t>
+          <t>Photo Guide resolver</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>LockCore runtime（產品層）</t>
+          <t>品牌照片樣本圖解析器</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>產品層 Turn 狀態機：恢復 session、組上下文、執行、儲存並產生一次回覆。</t>
+          <t>解析 AI 回覆文末的 photo-guide 標記、剝除內部標記並按設定附加 LINE ImageMessage；目前只核准 Chatlock 安裝前樣本圖。</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>編排一次對話 Turn；不直接實作通用 tool-using LLM 迴圈。</t>
+          <t>只呈現預先核准的品牌靜態圖片；不讀取或辨識客戶照片，也不允許未設定品牌自行附圖。</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>AGT·CHN、AGT·RES</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L138–149 ｜ 12_SAD §4.1 L145–148</t>
+          <t>AGT·CHN</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374 ｜ 15_SDS §5.1 L367–374; §5.3</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>AgentRunner</t>
+          <t>Quote postback message mapper</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>LockCore runtime（通用執行層）</t>
+          <t>報價回覆錯誤回覆內容分類器</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>通用 Agent 執行器：在有界迴圈內呼叫模型、處理 tool calls，並在每輪執行上下文治理。</t>
+          <t>依 QUOTE_EXPIRED、QUOTE_ALREADY_DECIDED、NOT_FOUND、FORBIDDEN 等 API error_code 產生對客戶可理解的 LINE 回覆。</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>不知道報價、派工等產品流程；產品狀態由 AgentLoop、Skill 與 API 約束。</t>
+          <t>只映射終態與錯誤回覆內容；報價狀態機、權限與冪等仍由品牌 API 執行。</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>AGT·CHN、AGT·GOV、AGT·RES</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L138–149 ｜ 12_SAD §4.1 L145–148 ｜ 12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>AGT·CHN</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374 ｜ 15_SDS §5.1 L367–374; §5.3 ｜ 15_SDS §5.1 L369–374; §5.4</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>ContextBuilder</t>
+          <t>WebhookIdempotencyStore</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>LockCore runtime（上下文層）</t>
+          <t>LINE webhook 冪等保留庫</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>上下文組裝器：依序組合 identity、Customer Memory、always-skills 與 skill 摘要。</t>
+          <t>在處理 LINE event 前以 mark-first 方式保留 event ID，重送時直接略過，避免重複回覆或建卡。</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>只建立模型輸入上下文；不負責永久儲存或模型供應商路由。</t>
+          <t>只治理 webhook 重播；不代替報價、工單與金流 mutation 的 Idempotency-Key。</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>AGT·CHN</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>LiteLLMProvider + FallbackProvider</t>
+          <t>AgentLoop</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LockCore runtime（產品層）</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>模型供應商層：以 model 字串路由多家 LLM，並在主供應商失敗時切換備援。</t>
+          <t>產品層 Turn 狀態機：恢復 session、組上下文、執行、儲存並產生一次回覆。</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>處理模型呼叫、重試與備援切換；不承載業務規則或產品決策。</t>
+          <t>編排一次對話 Turn；不直接實作通用 tool-using LLM 迴圈。</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>AGT·GOV、PLT·LLM</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407 ｜ 12_SAD §4.1 L146; §9 L395, L407</t>
+          <t>AGT·CHN、AGT·RES</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.2 L68; §5.1 L370; §13 L707 ｜ 15_SDS §5.1 L369–374; §5.4</t>
-        </is>
-      </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Model Orchestration Layer</t>
+          <t>AgentRunner</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LockCore runtime（通用執行層）</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>供應商無關的模型編排層：集中管理路由、備援處理、逾時、快取與呼叫效率。</t>
+          <t>通用 Agent 執行器：在有界迴圈內呼叫模型、處理 tool calls，並在每輪執行上下文治理。</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>是技術治理層，不是 Agent 產品流程、Skill 或知識庫。</t>
+          <t>不知道報價、派工等產品流程；產品狀態由 AgentLoop、Skill 與 API 約束。</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>PLT·LLM</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L146; §9 L395, L407</t>
+          <t>AGT·CHN、AGT·GOV、AGT·RES</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §2.2 L68; §5.1 L370; §13 L707</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3 ｜ 15_SDS §5.1、§5.4</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py ｜ agent/lockcore/channels/line_gateway.py; agent/lockcore/agent/{loop,runner}.py</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>ToolRegistry</t>
+          <t>ReplyGuard</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -10895,207 +10931,232 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Agent 工具登錄與允許清單：定義哪些工具可被模型呼叫，並治理呼叫邊界。</t>
+          <t>Agent 回覆出口守衛：攔截確定金額、錯誤型號、假稱已轉真人等違規輸出，必要時重生或轉人工。</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>不自行決定何時呼叫工具，也不向模型暴露未登錄的任意程式。</t>
+          <t>是模型輸出的最後安全層；不取代 API 的報價、派工與權限硬閘。</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>AGT·GOV、AGT·RES</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148 ｜ 12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>AGT·RES</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3 ｜ 15_SDS §5.1 L369–374; §5.4</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>MemoryManager + Store</t>
+          <t>SentimentClassifier</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>Memory</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>長期記憶管理與存儲層：載入/寫回客戶已確認事實，讀寫必須同帶 tenant_id + user_id。</t>
+          <t>在不阻斷主回覆的前提下判定負面情緒並產生警示所需資料。</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>不等於當次 session 原始對話，不可跨租戶或使用者共用。</t>
+          <t>只做情緒分類與旁路警示；不單獨決定報價、派工或工單狀態。</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>AGT·RES</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>EscalationStore</t>
+          <t>ContextBuilder</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LockCore runtime（上下文層）</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>轉真人稽核存儲：記錄轉接理由、已知事實快照與必要追溯資料。</t>
+          <t>上下文組裝器：依序組合 identity、Customer Memory、always-skills 與 skill 摘要。</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>保證轉人事件不遺漏；不是正式工單庫，也不代替 API 的開單 gate。</t>
+          <t>只建立模型輸入上下文；不負責永久儲存或模型供應商路由。</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>AGT·RES</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>SkillsLoader + 2 builtin skills</t>
+          <t>LiteLLMProvider + FallbackProvider</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Agent 行為規範載入器：載入 product-knowledge 與 cs-sop，定義判斷、查資料、轉真人與不可違反條件。</t>
+          <t>模型供應商層：以 model 字串路由多家 LLM，並在主供應商失敗時切換備援。</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>管「怎麼做」；不是長期對話記憶，也不是所有長尾事實的唯一資料庫。</t>
+          <t>處理模型呼叫、重試與備援切換；不承載業務規則或產品決策。</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>AGT·GOV、AGT·KNW、REF·PUB</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407 ｜ 12_SAD §4.1 L147–149 ｜ 12_SAD §4.4 L183–187</t>
+          <t>AGT·GOV、PLT·LLM</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374 ｜ 15_SDS §5.1 L369–374; §5.4 ｜ 15_SDS §9.1 L617–619; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/ ｜ agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ knowledge-pipeline/refinery/; agent/lockcore/skills/*/references/</t>
+          <t>12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §2.2、§5.1、§13 ｜ 15_SDS §5.1、§5.4</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>記憶 DB</t>
+          <t>Model Orchestration Layer</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Memory backend</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Agent 長期記憶的永久化後端，設計上使用 Postgres schema agent.*。</t>
+          <t>供應商無關的模型編排層：集中管理路由、備援處理、逾時、快取與呼叫效率。</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>只存 Agent 記憶與相關稽核；不是品牌業務庫、平台庫或技師權威庫。</t>
+          <t>是技術治理層，不是 Agent 產品流程、Skill 或知識庫。</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>AGT·KNW</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>PLT·LLM</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
+          <t>12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §2.2、§5.1、§13</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>agent/lockcore/providers/{litellm_provider,fallback_provider}.py</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>tenant-scoped routers</t>
+          <t>ToolRegistry</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -11105,81 +11166,91 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>以 /tenants/{tid}/... 暴露品牌業務的 FastAPI 路由層，負責 HTTP 入口、輸入驗證與授權依賴。</t>
+          <t>Agent 工具登錄與允許清單：定義哪些工具可被模型呼叫，並治理呼叫邊界。</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>不在 router 堆疊主要 SQL/業務邏輯；租戶與角色檢查交給標準守衛鏈。</t>
+          <t>不自行決定何時呼叫工具，也不向模型暴露未登錄的任意程式。</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>API·CASE</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>AGT·GOV、AGT·RES</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>api/routers/; api/services/; api/core/db.py</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3 ｜ 15_SDS §5.1、§5.4</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Service Layer（problem_card / quote）</t>
+          <t>MemoryManager + Store</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Memory</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>問題卡與報價服務層：管理診斷卡 gate、報價狀態、版本與不可否認快照。</t>
+          <t>長期記憶管理與存儲層：載入/寫回客戶已確認事實，讀寫必須同帶 tenant_id + user_id；預設 SQLite，可設定 PostgreSQL。</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>不讓 Agent 或技師端直接定價；品牌 API 仍是報價權威。</t>
+          <t>不等於當次 session 原始對話，不可跨租戶或使用者共用。</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>API·CASE</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>api/routers/; api/services/; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）</t>
+          <t>EscalationStore</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -11189,81 +11260,91 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>工單服務層：建立工單、驗狀態轉移/gate、寫入時間軸並觸發副作用。</t>
+          <t>轉真人稽核存儲：記錄轉接理由、已知事實快照與必要追溯資料。</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>不允許 AI 繞過客戶確認與人工審核直接轉工單。</t>
+          <t>保證轉人事件不遺漏；不是正式工單庫，也不代替 API 的開單 gate。</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>API·WO</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>AGT·RES</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>api/services/work_order_service.py; api/routers/; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§5.3</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/{loop,runner,tools}/; agent/lockcore/agent/user_memory/escalation.py</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）</t>
+          <t>SkillsLoader + 2 builtin skills</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Skills</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>派工服務層：執行候選查詢、指派、接單 SLA、擴大範圍與狀態更新。</t>
+          <t>Agent 行為規範載入器：載入 product-knowledge 與 cs-sop，定義判斷、查資料、轉真人與不可違反條件。</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>不在品牌庫雙寫技師權威資料；媒合應經 OHS 與事件契約。</t>
+          <t>管「怎麼做」；不是長期對話記憶，也不是所有長尾事實的唯一資料庫。</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>API·DISP</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>AGT·GOV、AGT·KNW、REF·PUB</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>api/services/dispatch*; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.1 ｜ 12_SAD §4.1、§9 ｜ 12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1 ｜ 15_SDS §5.1、§5.4 ｜ 15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/ ｜ agent/lockcore/agent/runner.py; agent/lockcore/providers/; agent/lockcore/agent/tools/; agent/lockcore/skills/ ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（invoice / settlement）</t>
+          <t>SkillSync</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -11273,81 +11354,91 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>帳單、收付、對帳與結算邏輯：管理金額狀態、冪等、reversal 與帳本一致性。</t>
+          <t>輪詢品牌庫已發布的 skill revision，以原子交換同步到 workspace overlay，讓新版本在執行期生效。</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Billing 真相留品牌側；跨品牌技師 Settlement 由 technician-platform 匯總。</t>
+          <t>只同步已發布版本且失敗時保留舊版；不自行核准 draft，也不覆寫平台保護層。</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>API·FIN</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>api/services/{invoice,settlement}*; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>core/db.py</t>
+          <t>記憶 DB</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Memory backend</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>API 資料庫基礎層：管理連線池、交易邊界與讀寫分離。</t>
+          <t>Agent 長期記憶的永久化後端，設計上使用 Postgres schema agent.*。</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>不放領域流程決策；業務交易應由 service 層呼叫。</t>
+          <t>只存 Agent 記憶與相關稽核；不是品牌業務庫、平台庫或技師權威庫。</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>API·CASE、API·FIN、API·WO、DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L151–164; §9 L397 ｜ 12_SAD §4.2 L151–164; §9 L401 ｜ 12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>AGT·KNW</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451 ｜ 15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466 ｜ 15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472 ｜ 15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql ｜ api/routers/; api/services/; api/core/db.py ｜ api/services/work_order_service.py; api/routers/; api/core/db.py ｜ api/services/{invoice,settlement}*; api/core/db.py</t>
+          <t>12_SAD §4.1</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>agent/lockcore/agent/context.py; agent/lockcore/agent/user_memory/; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>internal_ingest.py</t>
+          <t>tenant-scoped routers</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -11357,39 +11448,44 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>Agent 與內部服務使用的 /internal/* 入口，接收對話、轉人與報價回應等旁路資料。</t>
+          <t>以 /tenants/{tid}/... 暴露品牌業務的 FastAPI 路由層，負責 HTTP 入口、輸入驗證與授權依賴。</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>只接受驗證失敗即拒絕內部憑證；不是 LINE webhook 入站門。</t>
+          <t>不在 router 堆疊主要 SQL/業務邏輯；租戶與角色檢查交給標準守衛鏈。</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>API·INT</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>API·CASE</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service*</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>WebSocket 端點</t>
+          <t>Service Layer（problem_card / quote）</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -11399,81 +11495,91 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>經授權的即時推播連線入口，依 channel、技師與租戶將狀態更新送給前端。</t>
+          <t>問題卡與報價服務層：管理診斷卡 gate、報價狀態、版本與不可否認快照。</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>是即時通知管道，不是業務事件的永久真相；斷線時頁面應可退化為 REST。</t>
+          <t>不讓 Agent 或技師端直接定價；品牌 API 仍是報價權威。</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>API·INT、PLT·EVT、TEC·MATCH、TEC·PROJ</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394 ｜ 12_SAD §4.5 L189–197 ｜ 12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>API·CASE</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548 ｜ 15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677 ｜ 15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service* ｜ technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Redis pub/sub</t>
+          <t>Conversation media collector</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>對話照片掛卡器</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>跨實例的低延遲訊息擴散，用於 WebSocket fan-out、cache 與部分分散式鎖。</t>
+          <t>AI 建問題卡時反查同一對話近 24 小時內最多 5 張照片，依時間排序附加到 media_urls。</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>不保證長期持久與重播；需重播的事件應使用 Kafka 或資料庫。</t>
+          <t>只掛接已持久化媒體 URL，採 append-only 且查詢失敗略過；不做任何影像辨識。</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>API·DISP、API·INT、PLT·EVT</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L151–164; §8.1–8.2 L353–372 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394</t>
+          <t>API·CASE</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677 ｜ 15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service* ｜ api/services/dispatch*; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Service Layer（work_order）</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -11483,81 +11589,91 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>持久、可重播的跨系統事件骨幹，傳遞 technician.*、dispatch.*、workorder.* 與 commission.* 等事件。</t>
+          <t>工單服務層：建立工單、驗狀態轉移/gate、寫入時間軸並觸發副作用。</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>不代替低延遲同步查詢（OHS/REST），也不代替各領域真相資料庫。</t>
+          <t>不允許 AI 繞過客戶確認與人工審核直接轉工單。</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>API·DISP、API·FIN、API·INT、DAT·SYNC、PLT·EVT、TEC·SET</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164 ｜ 12_SAD §4.2 L151–164; §8.1–8.2 L353–372 ｜ 12_SAD §4.2 L151–164; §9 L401 ｜ 12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394 ｜ 12_SAD §4.5 L189–197; §9 L401</t>
+          <t>API·WO</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560 ｜ 15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677 ｜ 15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677 ｜ 15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677 ｜ 15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service* ｜ api/services/dispatch*; api/realtime/; Kafka integration ｜ api/services/{invoice,settlement}*; api/core/db.py ｜ knowledge-pipeline/; api/realtime/; Kafka integration ｜ technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>分散式排程</t>
+          <t>Consent link service</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>免責同意簽署連結服務</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>跨實例協調 SLA、GDPR 永久刪除、自動結案與 LINE outbox 等背景工作，並以鎖避免重複執行。</t>
+          <t>為工單產生公開簽署 token、保存 token hash 稽核並透過 LINE 推送；無 LINE 綁定時回傳可複製連結。</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>只觸發已定義任務；不把關鍵業務真相只留在 scheduler 記憶體。</t>
+          <t>只負責交付簽署入口與稽核；簽署內容、角色/租戶授權與結案 gate 仍由 API 驗證。</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>API·DISP、PLT·EVT</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372 ｜ 12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394</t>
+          <t>API·WO</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660 ｜ 15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>api/realtime/; Kafka/Redis integration ｜ api/services/dispatch*; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>line_push_service + outbox worker</t>
+          <t>Service Layer（dispatch）</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -11567,81 +11683,91 @@
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>LINE 出站推播與可重試佇列：業務交易先寫 outbox，worker 後送並記錄結果。</t>
+          <t>派工服務層：執行候選查詢、指派、接單 SLA、擴大範圍與狀態更新。</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>推播失敗不還原主業務寫入；不處理 LINE 入站 webhook。</t>
+          <t>不在品牌庫雙寫技師權威資料；媒合應經 OHS 與事件契約。</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>API·INT</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>API·DISP</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>api/routers/internal_ingest.py; api/realtime/; api/services/line_push_service*</t>
+          <t>12_SAD §4.2、§8</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>守衛鏈</t>
+          <t>dispatch_service candidate scoring</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>現行媒合評分器</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>API 授權鏈：get_current_user → require_tenant → role_required，加上 platform admin 與 internal token 邊界。</t>
+          <t>現行派工服務直接由技師權威資料評估技能、品牌授權、距離、評分、工作量與公平性，產生候選排序。</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>逐端點預設拒絕 enforce；不把前端隱藏按鈕當成安全控制。</t>
+          <t>這是共用 API codebase 的 interim 實作；目標 OHS/MatchingService 獨立服務邊界尚未拆出。</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>API·GOV、PLT·IAM、TEC·ID</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393 ｜ 12_SAD §4.5 L189–197 ｜ 12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>API·DISP、TEC·MATCH</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670 ｜ 15_SDS §6.1 L428–472; §6.4 L494–499 ｜ 15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py ｜ technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認） ｜ web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/ ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>core/errors.py</t>
+          <t>Service Layer（invoice / settlement）</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
@@ -11651,39 +11777,44 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>API 錯誤標準化元件：將例外轉為 RFC7807 problem+json 相容信封。</t>
+          <t>帳單、收付、對帳與結算邏輯：管理金額狀態、冪等、reversal 與帳本一致性。</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>統一錯誤呈現與分類；不吞掉必須中斷的安全或交易錯誤。</t>
+          <t>Billing 真相留品牌側；跨品牌技師 Settlement 由 technician-platform 匯總。</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>API·GOV</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>API·FIN</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>core/idempotency.py</t>
+          <t>core/db.py</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
@@ -11693,123 +11824,138 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Mutation 冪等控制：以 Idempotency-Key 辨識重播，避免重複開單、收款或狀態轉移。</t>
+          <t>API 資料庫基礎層：管理品牌庫、技師權威庫與平台庫的連線取得、交易邊界及安全備援處理。</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>只保護重播語意；不代替業務狀態機與資料庫唯一約束。</t>
+          <t>不放領域流程決策；業務交易應由 service 層呼叫。</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>API·GOV</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>API·CASE、API·FIN、API·WO、DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6 ｜ 12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1 ｜ 15_SDS §4.2、§4.6、§6.1 ｜ 15_SDS §4.2、§6.1、§7.3</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py ｜ api/routers/; api/services/{problem_card_service,quote_engine_service}.py; api/core/db.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Middleware</t>
+          <t>API_SURFACE router filter</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>API 部署面塑形器</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>FastAPI 橫切處理鏈：處理 CORS、Request ID、版本廢棄等全局請求/回應邏輯。</t>
+          <t>同一 FastAPI codebase 依 API_SURFACE=dispatch/tech/platform 裁切路由與背景 worker，形成三個可獨立部署面。</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>不承載單一領域的核心業務規則。</t>
+          <t>只縮小部署暴露面，不是授權邊界；每個保留端點仍須 RBAC、租戶或平台守衛。</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>API·GOV</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>API·GOV、TEC·ID</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
-        </is>
-      </c>
-      <c r="H31" s="11" t="inlineStr">
-        <is>
-          <t>api/core/{deps,errors,idempotency,auth,pii_crypto}.py; api/main.py</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>AuthGuard</t>
+          <t>Three-DB Connection Router</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>三庫連線路由</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>Web 根佈局的前端路由守衛：先做跨站導向，再檢查 token 與角色存取。</t>
+          <t>依資料權威將連線導向品牌庫、lock_tech 或 lock_platform，並可用 DB_URI_STRICT 阻止必要 URI 缺失時啟動。</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>只是 UX 層門禁；真正授權必須由 API 守衛鏈 enforce。</t>
+          <t>治理資料庫選擇與驗證失敗即拒絕；不代表 production migration 或 backfill 已完成。</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>WEB·SHELL</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
-        </is>
-      </c>
-      <c r="H32" s="13" t="inlineStr">
-        <is>
-          <t>web/src/components/layout/AuthGuard.tsx; web/src/lib/{appMode,rolePolicy}.ts</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>appMode gate</t>
+          <t>DBPoolScopeMiddleware</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -11819,81 +11965,91 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>判斷當前 portal build 是否服務某路徑，不屬於本站的路徑導向對應 portal。</t>
+          <t>在 request 生命週期建立與回收資料庫 pool scope，避免跨請求連線狀態滲漏。</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>是分站與導航控制，不是後端租戶或角色安全邊界。</t>
+          <t>只治理連線資源生命週期；不決定資料權威或業務交易內容。</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>WEB·SHELL</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
-        </is>
-      </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>web/src/components/layout/AuthGuard.tsx; web/src/lib/{appMode,rolePolicy}.ts</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>rolePolicy</t>
+          <t>DEKService + PII blind index + purge ledger</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>個資密鑰與清除稽核套件</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>前端 route→roles 最長前綴政策表，控制導航與無權使用者的安全落點。</t>
+          <t>以每使用者 DEK、blind index 與 append-only purge ledger 支援個資查找、加密、忘卻與清除證據。</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>只提供前端 UX 治理；不代替 API role_required。</t>
+          <t>程式與 migration 存在不等於正式 KEK、backfill 與 production 部署已驗證。</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>WEB·AUD、WEB·SHELL</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599 ｜ 15_SDS §8.1 L570–578</t>
-        </is>
-      </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>web/src/components/layout/AuthGuard.tsx; web/src/lib/{appMode,rolePolicy}.ts ｜ web/src/lib/{rolePolicy,api}.ts; web/types/api.generated.ts</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>api client</t>
+          <t>internal_ingest.py</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -11903,39 +12059,44 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Web 統一 HTTP client：注入 Bearer、X-Tenant-ID、Idempotency-Key，處理 refresh 與錯誤信封。</t>
+          <t>Agent 與內部服務使用的 /internal/* 入口，接收對話、轉人與報價回應等旁路資料。</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>不在瀏覽器內繞過 API 授權，也不將客戶端狀態當作服務端真相。</t>
+          <t>只接受驗證失敗即拒絕內部憑證；不是 LINE webhook 入站門。</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>WEB·AUD、WEB·CX、WEB·OPS</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·INT</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L570–578 ｜ 15_SDS §8.1 L575–578; §8.3 L593–599</t>
-        </is>
-      </c>
-      <c r="H35" s="11" t="inlineStr">
-        <is>
-          <t>web/src/lib/{api,cache,realtime}.ts ｜ web/src/lib/{rolePolicy,api}.ts; web/types/api.generated.ts</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>cache</t>
+          <t>WebSocket 端點</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
@@ -11945,39 +12106,44 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>Web GET 請求共享 in-flight 與短期 staleTime 快取，mutation 後可主動失效。</t>
+          <t>經授權的即時推播連線入口，依 channel、技師與租戶將狀態更新送給前端。</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>是前端效能優化；不是永久資料庫或授權依據。</t>
+          <t>是即時通知管道，不是業務事件的永久真相；斷線時頁面應可退化為 REST。</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·INT、PLT·EVT、TEC·MATCH、TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
-        </is>
-      </c>
-      <c r="H36" s="13" t="inlineStr">
-        <is>
-          <t>web/src/lib/{api,cache,realtime}.ts</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>realtime</t>
+          <t>Redis pub/sub</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -11987,39 +12153,44 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>WebSocket 訂閱層：一 channel 一 socket、處理重連 backoff，未設定時靜默降級。</t>
+          <t>跨實例的低延遲訊息擴散，用於 WebSocket fan-out、cache 與部分分散式鎖。</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>負責前端即時連線生命週期；不是事件持久層。</t>
+          <t>不保證長期持久與重播；需重播的事件應使用 Kafka 或資料庫。</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>WEB·CX、WEB·OPS</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·DISP、API·INT、PLT·EVT</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>web/src/lib/{api,cache,realtime}.ts</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>型別（api.generated.ts）</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
@@ -12029,39 +12200,44 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>由 OpenAPI 生成的 TypeScript API 型別，使前端在編譯期偵測契約漂移。</t>
+          <t>持久、可重播的跨系統事件骨幹；現行 producer/consumer 實作 topic 為 workorder.lifecycle、commission.accrued、technician.lifecycle。</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>反映契約但不定義業務真相；不手改生成檔來代替 OpenAPI。</t>
+          <t>不代替低延遲同步查詢（OHS/REST），也不代替各領域真相資料庫。</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>WEB·AUD</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>API·DISP、API·FIN、API·INT、DAT·SYNC、PLT·EVT、TEC·SET</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in） ｜ PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in） ｜ PARTIAL（Redis/Kafka 依部署設定啟用） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用） ｜ PARTIAL（跨系統事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L570–578</t>
-        </is>
-      </c>
-      <c r="H38" s="13" t="inlineStr">
-        <is>
-          <t>web/src/lib/{rolePolicy,api}.ts; web/types/api.generated.ts</t>
+          <t>12_SAD §4.2 ｜ 12_SAD §4.2、§4.6、§8.2 ｜ 12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §4.2、§6.1、§7.3 ｜ 15_SDS §6.1–6.3、§11 ｜ 15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1 ｜ 15_SDS §6.3–6.4、§9.3、§11 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py ｜ api/services/{invoice_service,settlement_service,reconciliation_service,technician_statement_service}.py; api/core/{db,event_bus}.py ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql ｜ knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>Medallion pipeline</t>
+          <t>EventBusProducer</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -12071,39 +12247,44 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>離線資料流水線：將素材依 raw→bronze→silver 分層處理，保留來源與可重現性。</t>
+          <t>將受控領域事件序列化並發布到 Kafka；未設定 KAFKA_BOOTSTRAP 時按設計不啟用。</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>是 batch 與持久資產，不是長駐即時 API runtime。</t>
+          <t>只發布已定義 topic 的事件；不保證所有設計中的萬用 wildcard topic 均已實作。</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>API·INT</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>source_to_raw</t>
+          <t>EventConsumerWorker</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
@@ -12113,39 +12294,44 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>收集原始外部素材並原樣實作到 raw 層，保留來源識別與取得資訊。</t>
+          <t>消費 Kafka 工單生命週期與佣金事件，使用 event_consumer_dedup 冪等更新技師 CQRS 投影。</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>不宣告內容已清洗或可直接用於 Agent 回答。</t>
+          <t>需 KAFKA_BOOTSTRAP 才啟動；不把 projection 當成品牌工單或計費的命令真相。</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>DAT·MED</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.6 L199–208</t>
+          <t>TEC·PROJ、TEC·SET</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H40" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+          <t>12_SAD §4.5、§8.2 ｜ 12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>raw_to_bronze</t>
+          <t>分散式排程</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -12155,39 +12341,44 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>將 raw 影音、網頁或文件轉錄與清洗為可審查的 bronze 素材。</t>
+          <t>跨實例協調 SLA、GDPR 永久刪除、自動結案與 LINE outbox 等背景工作，並以鎖避免重複執行。</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>只做可追溯轉換；不將未審核內容直接發布至知識庫。</t>
+          <t>只觸發已定義任務；不把關鍵業務真相只留在 scheduler 記憶體。</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>DAT·MED、REF·INTAKE</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L179–187 ｜ 12_SAD §4.6 L199–208</t>
+          <t>API·DISP、PLT·EVT</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用） ｜ PARTIAL（Redis/Kafka opt-in）</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635 ｜ 15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H41" s="11" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>12_SAD §4.2、§8 ｜ 12_SAD §4.2、§8–9</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.3、§11 ｜ 15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/; web/brand-portal/docker-compose.yml（events profile） ｜ api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>bronze_to_silver</t>
+          <t>PG Advisory Cron Leader</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -12197,39 +12388,44 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>將 bronze 去冗、糾錯、語意切塊成 silver，並由程式覆寫 provenance 防止 LLM 幻覺來源。</t>
+          <t>以 PostgreSQL advisory lock 選出單一排程 leader，避免多實例重複執行背景工作。</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>silver 不等於已核可發布；下游仍需提煉、人工審核與 Publisher gate。</t>
+          <t>只協調任務執行權；不取代任務本身的冪等、重試與稽核。</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>DAT·MED、REF·INTAKE</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L179–187 ｜ 12_SAD §4.6 L199–208</t>
+          <t>API·DISP</t>
+        </is>
+      </c>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka/Redis 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635 ｜ 15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>12_SAD §4.2、§8</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{dispatch_service,dispatch_log_service}.py; api/routers/dispatch_v2.py; api/realtime/; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>storage（raw/bronze/silver）</t>
+          <t>line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -12239,39 +12435,44 @@
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Medallion 各分層的持久檔案資產，保留原始、可審查與結構化中間成果。</t>
+          <t>LINE 出站推播與可重試佇列：業務交易先寫 outbox，worker 後送並記錄結果。</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>是 pipeline 資產庫；不等於線上 pgvector 查詢庫。</t>
+          <t>推播失敗不還原主業務寫入；不處理 LINE 入站 webhook。</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>DAT·MED</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.6 L199–208</t>
+          <t>API·INT</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Redis/Kafka 依部署設定啟用）</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L611–613; 附錄 L736</t>
-        </is>
-      </c>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
+          <t>12_SAD §4.2</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1–6.3、§11</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>api/routers/internal_ingest.py; api/realtime/; api/services/{line_push_service,line_push_outbox_service}.py; api/core/event_bus.py</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql</t>
+          <t>守衛鏈</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
@@ -12281,39 +12482,44 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>資料庫基底 schema 定義，描述主表、索引與基礎約束。</t>
+          <t>API 授權鏈：get_current_user → require_tenant → role_required，加上 platform admin 與 internal token 邊界。</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>不直接代替已上線環境的 forward-only migration 演進記錄。</t>
+          <t>逐端點預設拒絕 enforce；不把前端隱藏按鈕當成安全控制。</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>API·GOV、PLT·IAM、TEC·ID</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase） ｜ PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
-        </is>
-      </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql</t>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§9 ｜ 12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2 ｜ 15_SDS §6.1、§6.4 ｜ 15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/ ｜ web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>forward-only migrations</t>
+          <t>core/errors.py</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
@@ -12323,39 +12529,44 @@
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>只向前套用、有順序與可稽核性的 SQL schema 變更集。</t>
+          <t>API 錯誤標準化元件：將例外轉為 RFC7807 problem+json 相容信封。</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>不靠手改 production schema；漂移與重複套用必須由 CI/測試阻擋。</t>
+          <t>統一錯誤呈現與分類；不吞掉必須中斷的安全或交易錯誤。</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
-        </is>
-      </c>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>platform schema</t>
+          <t>core/idempotency.py</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
@@ -12365,39 +12576,44 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>平台治理庫的獨立 schema，存管理員、品牌申請等跨租戶管理資料。</t>
+          <t>Mutation 冪等控制：以 Idempotency-Key 辨識重播，避免重複開單、收款或狀態轉移。</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>不存單一品牌內的工單、客戶或報價真相。</t>
+          <t>只保護重播語意；不代替業務狀態機與資料庫唯一約束。</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>DAT·SCH</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
-        </is>
-      </c>
-      <c r="H46" s="13" t="inlineStr">
-        <is>
-          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/platform/Schema_platform.sql</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>MCP RAG server</t>
+          <t>Middleware</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -12407,39 +12623,44 @@
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>以 MCP 工具契約向 Agent 暴露產品手冊與相似案例的租戶授權檢索服務。</t>
+          <t>FastAPI 橫切處理鏈：處理 CORS、Request ID、版本廢棄等全局請求/回應邏輯。</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>只負責事實檢索；不定義 Agent 行為，也不允許無 tenant ACL 直查 DB。</t>
+          <t>不承載單一領域的核心業務規則。</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>DAT·RAG</t>
-        </is>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §8.1 L353–361; §9 L407</t>
+          <t>API·GOV</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677</t>
-        </is>
-      </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>rag MCP service; SQL migrations; knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.2、§9</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§6.4</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>api/main.py; api/core/{deps,errors,idempotency,auth,pii_crypto,db}.py</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>品牌庫 pgvector</t>
+          <t>AuthGuard</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
@@ -12449,39 +12670,44 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>每品牌物理隔離的 PostgreSQL/pgvector，存業務資料與該品牌唯一事實語料。</t>
+          <t>Web 根佈局的前端路由守衛：先做跨站導向，再檢查 token 與角色存取。</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>不跨品牌共用記錄；技師權威資料仍在 lock_tech。</t>
+          <t>只是 UX 層門禁；真正授權必須由 API 守衛鏈 enforce。</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>DAT·RAG、REF·PUB</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187 ｜ 12_SAD §8.1 L353–361; §9 L407</t>
+          <t>WEB·SHELL</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677 ｜ 15_SDS §9.1 L617–619; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/; agent/lockcore/skills/*/references/ ｜ rag MCP service; SQL migrations; knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1–8.3</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>rag_manual_chunks / case_entries</t>
+          <t>appMode gate</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
@@ -12491,39 +12717,44 @@
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>RAG 的手冊切塊與案例條目，帶租戶/品牌過濾、embedding 與 provenance。</t>
+          <t>判斷當前 portal build 是否服務某路徑，不屬於本站的路徑導向對應 portal。</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>是被查找的事實資料；不是 Skill 行為規範或對話 Memory。</t>
+          <t>是分站與導航控制，不是後端租戶或角色安全邊界。</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>DAT·RAG</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §8.1 L353–361; §9 L407</t>
+          <t>WEB·SHELL</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677</t>
-        </is>
-      </c>
-      <c r="H49" s="11" t="inlineStr">
-        <is>
-          <t>rag MCP service; SQL migrations; knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1–8.3</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>outbox</t>
+          <t>rolePolicy</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
@@ -12533,39 +12764,44 @@
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>與主業務交易同步寫入的待發送記錄，由 worker 重試投遞通知或事件。</t>
+          <t>前端 route→roles 最長前綴政策表，控制導航與無權使用者的安全落點。</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>解耦交易與外部副作用；不代替 Kafka 的跨系統長期事件紀錄。</t>
+          <t>只提供前端 UX 治理；不代替 API role_required。</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>WEB·AUD、WEB·SHELL</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（OIDC cookie 與 legacy token 過渡）</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1 ｜ 15_SDS §8.1–8.3</t>
+        </is>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts ｜ web/{brand-portal,tech-portal,landing,platform-console}/src/components/layout/AuthGuard.tsx; 各站 src/lib/{appMode,rolePolicy}.ts</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>provenance / audit</t>
+          <t>api client</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -12575,123 +12811,138 @@
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>記錄資料來源、處理版本、行為者與時間的可重現與稽核證據。</t>
+          <t>Web 統一 HTTP client：注入 Bearer、X-Tenant-ID、Idempotency-Key，處理 refresh 與錯誤信封。</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>不允許 LLM 自行編造來源，也不把一般顯示紀錄當成不可否認稽核鏈。</t>
+          <t>不在瀏覽器內繞過 API 授權，也不將客戶端狀態當作服務端真相。</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>DAT·SYNC</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>WEB·AUD、WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
-        </is>
-      </c>
-      <c r="H51" s="11" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/; api/realtime/; Kafka integration</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1 ｜ 15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx} ｜ web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>汲取層</t>
+          <t>AuthImage / AuthImageLightbox</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>需認證媒體縮圖與預覽</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>知識精煉入口：收集 knowledge_ready 診斷卡與外部產品素材。</t>
+          <t>對相對媒體 URL 以 Bearer + X-Tenant-ID fetch 後建立 Blob URL，統一呈現縮圖、錯誤佔位與放大預覽。</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>只撿取符合租戶與完整度 gate 的輸入；不直接發布到 Agent。</t>
+          <t>只在品牌後台呈現受保護圖片；不把 token 放進 img src，也不繞過媒體 API 授權。</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>REF·INTAKE</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L179–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F52" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H52" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>提煉分流器</t>
+          <t>ConsentPanel</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>工單免責同意面板</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>將 silver 內容分為「可查找的事實」與「Agent 怎麼做的行為」兩條軌。</t>
+          <t>品牌工作台顯示三段免責同意狀態，並讓授權人員發送或複製客戶簽署連結。</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>只產生 draft；未經人工審核核可不得寫入 pgvector 或 Skill。</t>
+          <t>是操作與狀態顯示元件；不在前端自行判定簽署有效性或結案。</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>REF·REFINE</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L614–615; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Draft Queue</t>
+          <t>cache</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
@@ -12701,39 +12952,44 @@
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>事實 draft 與行為 diff 的審核佇列，包含來源、冪等鍵與狀態機。</t>
+          <t>Web GET 請求共享 in-flight 與短期 staleTime 快取，mutation 後可主動失效。</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>是待審產物，不是已發布知識。</t>
+          <t>是前端效能優化；不是永久資料庫或授權依據。</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>REF·人工審核、REF·REFINE</t>
-        </is>
-      </c>
-      <c r="F54" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L614–615; §9.3 L631–635 ｜ 15_SDS §9.1 L615–616; §9.2 L621–629</t>
-        </is>
-      </c>
-      <c r="H54" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>審核 UI backend</t>
+          <t>realtime</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
@@ -12743,39 +12999,44 @@
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>提供 draft 狀態轉移、diff 呈現、核可、駁回與 re-refine 的人工審核後端。</t>
+          <t>WebSocket 訂閱層：一 channel 一 socket、處理重連 backoff，未設定時靜默降級。</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>不自動把 LLM 產物當真相；核可與發布仍是兩個可稽核步驟。</t>
+          <t>負責前端即時連線生命週期；不是事件持久層。</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>REF·人工審核</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·CX、WEB·OPS</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L615–616; §9.2 L621–629</t>
-        </is>
-      </c>
-      <c r="H55" s="11" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1、§8.3</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx,app/consent/} ｜ web/brand-portal/src/{lib/,components/media/AuthImage.tsx,components/work-orders/DispatchOrderView.tsx}</t>
         </is>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>型別（api.generated.ts）</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
@@ -12785,39 +13046,44 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>核可後的雙軌發布器：事實 embed 後寫 pgvector；行為產生 append-only Skill patch/產出檔。</t>
+          <t>由 OpenAPI 生成的 TypeScript API 型別，使前端在編譯期偵測契約漂移。</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>只發布 approved draft；不跳過 provenance、tenant 過濾或人工審核 gate。</t>
+          <t>反映契約但不定義業務真相；不手改生成檔來代替 OpenAPI。</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>REF·PUB</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>WEB·AUD</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L617–619; §9.3 L631–635</t>
-        </is>
-      </c>
-      <c r="H56" s="13" t="inlineStr">
-        <is>
-          <t>knowledge-pipeline/refinery/; agent/lockcore/skills/*/references/</t>
+          <t>12_SAD §4.3</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §8.1</t>
+        </is>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,platform-console}/src/lib/{rolePolicy,api}.ts; 各站 src/types/api.generated.ts</t>
         </is>
       </c>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>self-service routers</t>
+          <t>Medallion pipeline</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
@@ -12827,39 +13093,44 @@
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>技師端自助 API：註冊、profile、技能/品牌授權、認證上傳、排班與工作台。</t>
+          <t>離線資料流水線：將素材依 raw→bronze→silver 分層處理，保留來源與可重現性。</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>只服務已驗證的技師生命週期；不暴露跨租戶品牌內部資料。</t>
+          <t>是 batch 與持久資產，不是長駐即時 API runtime。</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·SYNC</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H57" s="11" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>technician_service</t>
+          <t>source_to_raw</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
@@ -12869,39 +13140,44 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>技師身分、技能、品牌授權、停復權與評分等核心領域服務。</t>
+          <t>收集原始外部素材並原樣實作到 raw 層，保留來源識別與取得資訊。</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>真相寫入 lock_tech；不雙寫各品牌庫。</t>
+          <t>不宣告內容已清洗或可直接用於 Agent 回答。</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
         </is>
       </c>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>certification/kyc_service</t>
+          <t>raw_to_bronze</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
@@ -12911,39 +13187,44 @@
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>技師 KYC 與認證申請/審核服務，對敏感欄位加密並控制准入。</t>
+          <t>將 raw 影音、網頁或文件轉錄與清洗為可審查的 bronze 素材。</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>未核可或已失效認證不得進入媒合候選集。</t>
+          <t>只做可追溯轉換；不將未審核內容直接發布至知識庫。</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED、REF·INTAKE</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H59" s="11" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>lock_tech</t>
+          <t>bronze_to_silver</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
@@ -12953,39 +13234,44 @@
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>跨品牌技師身分域的獨立權威資料庫，存身分、技能、授權、排班、評分與結算 profile。</t>
+          <t>將 bronze 去冗、糾錯、語意切塊成 silver，並由程式覆寫 provenance 防止 LLM 幻覺來源。</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>不存各品牌的完整工單或客戶敏感資料。</t>
+          <t>silver 不等於已核可發布；下游仍需提煉、人工審核與 Publisher gate。</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>TEC·ID</t>
-        </is>
-      </c>
-      <c r="F60" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED、REF·INTAKE</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
-        </is>
-      </c>
-      <c r="H60" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3 ｜ 15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/ ｜ knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>OHS API routers</t>
+          <t>storage（raw/bronze/silver）</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
@@ -12995,39 +13281,44 @@
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>品牌 API 查詢技師共享池的同步契約入口，包含技師查詢、媒合、排班與認證查詢。</t>
+          <t>Medallion 各分層的持久檔案資產，保留原始、可審查與結構化中間成果。</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>主要做低延遲讀/媒合；指派與接單真相經業務命令及 Kafka 事件收斂。</t>
+          <t>是 pipeline 資產庫；不等於線上 pgvector 查詢庫。</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
-        </is>
-      </c>
-      <c r="F61" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·MED</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
-        </is>
-      </c>
-      <c r="H61" s="11" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.6</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1；附錄</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/; knowledge-pipeline/storage/</t>
         </is>
       </c>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>matching_service</t>
+          <t>SQL/Schema*.sql</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
@@ -13037,39 +13328,44 @@
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>依技能、地區、品牌授權、認證、可用性、評分與工作量排序技師候選。</t>
+          <t>資料庫基底 schema 定義，描述主表、索引與基礎約束。</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>回傳候選不等於已指派；不繞過 active、授權與認證 gate。</t>
+          <t>不直接代替已上線環境的 forward-only migration 演進記錄。</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
-        </is>
-      </c>
-      <c r="F62" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
-        </is>
-      </c>
-      <c r="H62" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1</t>
+        </is>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
         </is>
       </c>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>schedule_service</t>
+          <t>forward-only migrations</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
@@ -13079,39 +13375,44 @@
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>管理技師排班、可用時段、接單後工作量與行程狀態。</t>
+          <t>只向前套用、有順序與可稽核性的 SQL schema 變更集。</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>不直接決定品牌工單狀態；跨系統變更經事件與投影對齊。</t>
+          <t>不靠手改 production schema；漂移與重複套用必須由 CI/測試阻擋。</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>TEC·MATCH</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
-        </is>
-      </c>
-      <c r="H63" s="11" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
         </is>
       </c>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>事件層</t>
+          <t>platform schema</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
@@ -13121,39 +13422,44 @@
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>technician-platform 的 Kafka producer/consumer 與投影更新層，發技師狀態並收派工、工單與結算事件。</t>
+          <t>平台治理庫的獨立 schema，存管理員、品牌申請等跨租戶管理資料。</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>只以契約事件跨界；不直接連線或改寫品牌庫。</t>
+          <t>不存單一品牌內的工單、客戶或報價真相。</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>TEC·MATCH、TEC·PROJ</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197 ｜ 12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>DAT·SCH</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548 ｜ 15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H64" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1</t>
+        </is>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>技師工單 read-model</t>
+          <t>MCP RAG server</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
@@ -13163,39 +13469,44 @@
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>由品牌 workorder.* 事件建立的最小化 CQRS 查詢投影，供技師工作台顯示。</t>
+          <t>以 MCP 工具契約向 Agent 暴露產品手冊與相似案例的租戶授權檢索服務。</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>只複製任務所需欄位；不是工單命令真相，不複製品牌完整敏感資料。</t>
+          <t>只負責事實檢索；不定義 Agent 行為，也不允許無 tenant ACL 直查 DB。</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>TEC·PROJ、TEC·SET</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197; §9 L401 ｜ 12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>DAT·RAG</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660 ｜ 15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H65" s="11" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §5、§8–9</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
         </is>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>commission_settlement_service</t>
+          <t>品牌庫 pgvector</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
@@ -13205,39 +13516,44 @@
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>匯總各品牌 commission.accrued，建立技師跨品牌 statement、payout 與期末對帳。</t>
+          <t>每品牌物理隔離的 PostgreSQL/pgvector，存業務資料與該品牌唯一事實語料。</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>不重算品牌工單的 Billing 明細；差異以 reconcile gate 收斂。</t>
+          <t>不跨品牌共用記錄；技師權威資料仍在 lock_tech。</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>TEC·SET</t>
-        </is>
-      </c>
-      <c r="F66" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.5 L189–197; §9 L401</t>
+          <t>DAT·RAG、REF·PUB</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理） ｜ PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
-        </is>
-      </c>
-      <c r="H66" s="13" t="inlineStr">
-        <is>
-          <t>technician-platform 獨立 codebase（SDS 附錄 L738 尚待確認）</t>
+          <t>12_SAD §4.4 ｜ 12_SAD §5、§8–9</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§9.1、§11.3 ｜ 15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py ｜ knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>Casdoor</t>
+          <t>rag_manual_chunks / case_entries</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
@@ -13247,39 +13563,44 @@
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>集中式 IdP 與開通治理：提供 OIDC、租戶 org、角色 claims 與 License subscription。</t>
+          <t>RAG 的手冊切塊與案例條目，帶租戶/品牌過濾、embedding 與 provenance。</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>發行身分與角色資訊；資源層授權仍由各 API 預設拒絕 enforce。</t>
+          <t>是被查找的事實資料；不是 Skill 行為規範或對話 Memory。</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
-        </is>
-      </c>
-      <c r="F67" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>DAT·RAG</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（RAG_TENANT_ID opt-in）</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
-        </is>
-      </c>
-      <c r="H67" s="11" t="inlineStr">
-        <is>
-          <t>web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §5、§8–9</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>agent/rag/rag/; SQL/Schema_rag.sql; knowledge-pipeline/refinery/refinery/{publisher,embedding}.py</t>
         </is>
       </c>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>平台維運 console</t>
+          <t>outbox</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
@@ -13289,39 +13610,44 @@
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>Super Admin 使用的中央管理前端，處理品牌申請、租戶治理、License 與跨品牌營運視角。</t>
+          <t>與主業務交易同步寫入的待發送記錄，由 worker 重試投遞通知或事件。</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>不當作單品牌日常派工後台，也不繞過 platform admin 授權。</t>
+          <t>解耦交易與外部副作用；不代替 Kafka 的跨系統長期事件紀錄。</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>DAT·SYNC</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
-        </is>
-      </c>
-      <c r="H68" s="13" t="inlineStr">
-        <is>
-          <t>web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+        </is>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>License provisioning</t>
+          <t>provenance / audit</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -13331,39 +13657,44 @@
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>License 核准後部署 per-brand bundle、建品牌庫、綁 LINE channel/設定並做健康檢查。</t>
+          <t>記錄資料來源、處理版本、行為者與時間的可重現與稽核證據。</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>是開通與部署流程；不代替應用內租戶授權與資料隔離。</t>
+          <t>不允許 LLM 自行編造來源，也不把一般顯示紀錄當成不可否認稽核鏈。</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>PLT·IAM</t>
-        </is>
-      </c>
-      <c r="F69" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>DAT·SYNC</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in）</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
-        </is>
-      </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>web/platform-console; api platform surface; Casdoor deployment/config</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/pipeline/silver_to_knowledge/; api/core/event_bus.py; api/realtime/event_consumer.py; api/services/line_push_outbox_service.py</t>
         </is>
       </c>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>SigNoz</t>
+          <t>汲取層</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
@@ -13373,39 +13704,44 @@
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>平台系統可觀測性服務，收集 OpenTelemetry metrics、logs、traces 並提供 dashboard 與警示。</t>
+          <t>知識精煉入口：收集 knowledge_ready 診斷卡與外部產品素材。</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>看服務健康與系統行為；不專職管理 prompt 或模型 eval。</t>
+          <t>只撿取符合租戶與完整度 gate 的輸入；不直接發布到 Agent。</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
-        </is>
-      </c>
-      <c r="F70" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>REF·INTAKE</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（批次 CLI，尚無排程部署）</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
-        </is>
-      </c>
-      <c r="H70" s="13" t="inlineStr">
-        <is>
-          <t>集中共用可觀測性部署（非單一應用路徑）</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H70" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{intake,run_intake,entitlement}.py; knowledge-pipeline/pipeline/{raw_to_bronze,bronze_to_silver}/</t>
         </is>
       </c>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>OPIK</t>
+          <t>提煉分流器</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -13415,39 +13751,44 @@
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Agent LLM Ops 工具，追蹤 prompt、LLM trace、token/成本與 eval 品質。</t>
+          <t>將 silver 內容分為「可查找的事實」與「Agent 怎麼做的行為」兩條軌。</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>專注 AI 呼叫品質；不代替 SigNoz 的全系統可觀測性。</t>
+          <t>只產生 draft；未經人工審核核可不得寫入 pgvector 或 Skill。</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
-        </is>
-      </c>
-      <c r="F71" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>REF·REFINE</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（服務已實作，部署流程未完整）</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
-        </is>
-      </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>集中共用可觀測性部署（非單一應用路徑）</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py</t>
         </is>
       </c>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>OpenTelemetry</t>
+          <t>Draft Queue</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
@@ -13457,39 +13798,44 @@
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>服務不綁供應商的 metrics、logs、traces 儀表化與傳輸標準。</t>
+          <t>事實 draft 與行為 diff 的審核佇列，包含來源、冪等鍵與狀態機。</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>是觀測資料契約與傳輸層；不是 dashboard 或業務稽核帳本本身。</t>
+          <t>是待審產物，不是已發布知識。</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>PLT·OBS</t>
-        </is>
-      </c>
-      <c r="F72" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>REF·人工審核、REF·REFINE</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定） ｜ PARTIAL（服務已實作，部署流程未完整）</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
-        </is>
-      </c>
-      <c r="H72" s="13" t="inlineStr">
-        <is>
-          <t>集中共用可觀測性部署（非單一應用路徑）</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H72" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1–9.2 ｜ 15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{refine,store}.py ｜ knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>Flow DSL executor</t>
+          <t>審核 UI backend</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -13499,39 +13845,44 @@
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>讀取 Vertical Pack 的宣告式 flow，驗 guard、執行 block、持久化狀態/事件並掛 SLA timer。</t>
+          <t>提供 draft 狀態轉移、diff 呈現、核可、駁回與 re-refine 的人工審核後端。</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>只執行可驗證 DSL；拒絕任意 inline code，也不把 UI 編輯器當執行後端。</t>
+          <t>不自動把 LLM 產物當真相；核可與發布仍是兩個可稽核步驟。</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>API·WO、PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F73" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L397 ｜ 12_SAD §9 L396–398</t>
+          <t>REF·人工審核</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644 ｜ 15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
-        </is>
-      </c>
-      <c r="H73" s="11" t="inlineStr">
-        <is>
-          <t>api/services/work_order_service.py; api/routers/; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1–9.2</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>domain blocks / primitives</t>
+          <t>Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
@@ -13541,39 +13892,44 @@
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>雙層工單積木：對外是派工/報價/收款等粗顆粒 block，內部由查資料、轉狀態、發事件等 primitive 組合。</t>
+          <t>Refinery 審核服務可依環境使用 Casdoor RS256 OIDC 驗證 reviewer claims，並保留 HS256 過渡模式。</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>每顆積木必須有 inputs/preconditions/guards/effects 契約；不允許無法靜態驗證的自由腳本。</t>
+          <t>只驗證審核者身分與角色；compose 未提供 OIDC 設定時不可宣稱已完成正式切換。</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>API·WO、PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F74" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §4.2 L151–164; §9 L397 ｜ 12_SAD §9 L396–398</t>
+          <t>REF·人工審核</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（OIDC 可用，compose 仍採過渡設定）</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644 ｜ 15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
-        </is>
-      </c>
-      <c r="H74" s="13" t="inlineStr">
-        <is>
-          <t>api/services/work_order_service.py; api/routers/; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1–9.2</t>
+        </is>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{service,review,oidc}.py; knowledge-pipeline/refinery/static/index.html</t>
         </is>
       </c>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>Vertical Pack</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -13583,39 +13939,44 @@
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>可版本化的產業設定包，組合 field metadata、flow、catalog、knowledge、UI composition 與 blocks。</t>
+          <t>核可後的雙軌發布器：事實 embed 後寫 pgvector；行為產生 append-only Skill patch/產出檔。</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>承載產業/品牌差異；不改寫身分、金流、事件等平台不變核心。</t>
+          <t>只發布 approved draft；不跳過 provenance、tenant 過濾或人工審核 gate。</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>PLT·CFG、PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396, L398, L400 ｜ 12_SAD §9 L396–398</t>
+          <t>REF·PUB</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644 ｜ 15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
-        </is>
-      </c>
-      <c r="H75" s="11" t="inlineStr">
-        <is>
-          <t>待 M4 實作；目前為 SDS 設計元件 ｜ 待 M4/M5 實作；目前為 SAD/ADR/SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>FlowEditor</t>
+          <t>behavior patch artifact</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -13625,39 +13986,44 @@
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>對 flow DSL 進行拖拉或表單編輯的薄 UI，輸出仍是可版控、可驗證的 DSL。</t>
+          <t>行為軌核可後產生 target_path + content 的受控產出檔，保存於 draft provenance，交由 apply CLI 消費。</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>不直接執行任意程式；金流、派工與同意書仍受保護層及人工審核 gate。</t>
+          <t>產出檔仍不是已發布 skill；必須經 LiveSkill draft/人工發布或明確 git 備援處理才生效。</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>PLT·FLOW</t>
-        </is>
-      </c>
-      <c r="F76" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396–398</t>
+          <t>REF·PUB</t>
+        </is>
+      </c>
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644</t>
-        </is>
-      </c>
-      <c r="H76" s="13" t="inlineStr">
-        <is>
-          <t>待 M4 實作；目前為 SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry</t>
+          <t>LiveSkill DB ingest</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -13667,84 +14033,1363 @@
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>管理 skill、RAG 權限、prompt、品牌設定與版本/分階段發布的中央設定能力。</t>
+          <t>apply_behavior 預設呼叫 internal skills ingest，將核可產出檔以加性合併建立品牌 skill draft，再由後台人工發布。</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>租戶只可改客製層；安全、金額、工具允許清單等保護層不可 override。</t>
+          <t>需要 LOCK_API_BASE_URL 與 INTERNAL_API_TOKEN；缺少時只可走明確標示的 git 備援處理。</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>PLT·CFG</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396, L398, L400</t>
+          <t>REF·PUB</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（LiveSkill 預設路徑需 token；git 為備援處理）</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
-        </is>
-      </c>
-      <c r="H77" s="11" t="inlineStr">
-        <is>
-          <t>待 M4/M5 實作；目前為 SAD/ADR/SDS 設計元件</t>
+          <t>12_SAD §4.4</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §9.1、§9.3</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>knowledge-pipeline/refinery/refinery/{publisher,apply_behavior,embedding}.py; api/routers/internal_skills.py; agent/lockcore/skills/</t>
         </is>
       </c>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="13" t="inlineStr">
         <is>
+          <t>self-service routers</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>技師端自助 API：註冊、profile、技能/品牌授權、認證上傳、排班與工作台。</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>只服務已驗證的技師生命週期；不暴露跨租戶品牌內部資料。</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>technician_service</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>技師身分、技能、品牌授權、停復權與評分等核心領域服務。</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>真相寫入 lock_tech；不雙寫各品牌庫。</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>certification/kyc_service</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>技師 KYC 與認證申請/審核服務，對敏感欄位加密並控制准入。</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>未核可或已失效認證不得進入媒合候選集。</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>lock_tech</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>跨品牌技師身分域的獨立權威資料庫，存身分、技能、授權、排班、評分與結算 profile。</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>不存各品牌的完整工單或客戶敏感資料。</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>TEC·ID</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>OHS API routers</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>品牌 API 查詢技師共享池的同步契約入口，包含技師查詢、媒合、排班與認證查詢。</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>主要做低延遲讀/媒合；指派與接單真相經業務命令及 Kafka 事件收斂。</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>TEC·MATCH</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>schedule_service</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>管理技師排班、可用時段、接單後工作量與行程狀態。</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>不直接決定品牌工單狀態；跨系統變更經事件與投影對齊。</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>TEC·MATCH</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
+        </is>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>事件層</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
+        <is>
+          <t>technician-platform 的 Kafka producer/consumer 與投影更新層，發技師狀態並收派工、工單與結算事件。</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>只以契約事件跨界；不直接連線或改寫品牌庫。</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>TEC·MATCH、TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F84" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應） ｜ PARTIAL（媒合已實作；獨立 OHS 邊界未拆）</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H84" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §4.4、§7.1–7.2 ｜ 15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/ ｜ api/routers/{dispatch_v2,technicians_v2}.py; api/services/{dispatch_service,technician_schedule_service}.py; api/realtime/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>technician_workorder_projection</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>lock_tech 中由 workorder.lifecycle 事件維護的技師工單最小化投影。</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>只供技師查詢且 Kafka opt-in；不取代品牌工單真相，也尚未證明所有畫面都只讀此投影。</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>技師工單 read-model</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>由品牌 workorder.* 事件建立的最小化 CQRS 查詢投影，供技師工作台顯示。</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="inlineStr">
+        <is>
+          <t>只複製任務所需欄位；不是工單命令真相，不複製品牌完整敏感資料。</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>TEC·PROJ</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Kafka opt-in；畫面尚非全由投影供應）</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§8.2</t>
+        </is>
+      </c>
+      <c r="H86" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>api/core/event_bus.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>technician_commission_projection</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>lock_tech 中由 commission.accrued 事件維護的技師佣金 CQRS 投影。</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>只在 Kafka consumer 啟用時更新；不等於完整跨品牌 payout 已完成。</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>TEC·SET</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+        </is>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>technician settlement services</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>現行技師佣金、statement 與 reconciliation 服務集合，提供逐案佣金與對帳視圖。</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>目前為 partial/interim；不宣稱不存在的單一 commission_settlement_service 或完整跨品牌出款已實作。</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>TEC·SET</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（投影與跨品牌事件依 Kafka 啟用）</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §4.5、§9</t>
+        </is>
+      </c>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
+        </is>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{technician_commission_service,technician_statement_service,reconciliation_service,reconciliation_v2_service}.py; api/realtime/event_consumer.py; SQL/tech_authority/Schema_cqrs_projection.sql</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>Tech DB router + mirror</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>技師權威庫路由與相容鏡射</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>以 TECH_POSTGRES_URI 將技師身分寫入 lock_tech，並在過渡期按順序鏡射必要相容列到品牌側。</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>lock_tech 才是技師權威；鏡射是 interim 相容機制，不是長期雙寫架構。</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>DAT·SCH、TEC·ID</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ AS-BUILT（獨立部署 stack／共用 api codebase）</t>
+        </is>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§4.5 ｜ 12_SAD §4.2、§4.6</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §3.1、§6.1 ｜ 15_SDS §6.1、§7.1–7.2</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>SQL/Schema*.sql; SQL/migrations/*.sql; SQL/{platform,tech_authority}/; api/core/{db,tech_mirror}.py ｜ api/main.py; api/routers/{technicians_v2,platform_technicians,technician_certifications_v2,technician_lifecycle_v2}.py; api/services/technician_{service,kyc_service,certification_service,lifecycle_service}.py; api/core/{db,tech_mirror}.py; SQL/tech_authority/; web/tech-portal/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>Casdoor</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>集中式 IdP 與開通治理：提供 OIDC、租戶 org、角色 claims 與 License subscription。</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>發行身分與角色資訊；資源層授權仍由各 API 預設拒絕 enforce。</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G90" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H90" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>License Entitlement Gate</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>依平台庫 tenant license entitlement 判定租戶是否可使用選購能力；正式環境缺設定應驗證失敗即拒絕。</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>是應用層授權檢查；不等於部署 per-brand bundle 的環境開通設定自動化。</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="36" customHeight="1">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>平台維運 console</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>Super Admin 使用的中央管理前端，處理品牌申請、租戶治理、License 與跨品牌營運視角。</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>不當作單品牌日常派工後台，也不繞過 platform admin 授權。</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G92" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H92" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>License provisioning</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>License 核准後部署 per-brand bundle、建品牌庫、綁 LINE channel/設定並做健康檢查。</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>是開通與部署流程；不代替應用內租戶授權與資料隔離。</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>PLT·IAM</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（Casdoor/config 存在；環境開通設定未完整）</t>
+        </is>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2–8.3、§9</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>web/platform-console/; api/main.py（API_SURFACE=platform）; infra/casdoor/; web/platform-console/docker-compose.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="36" customHeight="1">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>SigNoz</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>平台系統可觀測性服務，收集 OpenTelemetry metrics、logs、traces 並提供 dashboard 與警示。</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>看服務健康與系統行為；不專職管理 prompt 或模型 eval。</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="36" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>OPIK</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>Agent LLM Ops 工具，追蹤 prompt、LLM trace、token/成本與 eval 品質。</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>專注 AI 呼叫品質；不代替 SigNoz 的全系統可觀測性。</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>OpenTelemetry</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>服務不綁供應商的 metrics、logs、traces 儀表化與傳輸標準。</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>是觀測資料契約與傳輸層；不是 dashboard 或業務稽核帳本本身。</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H96" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>PIIScrubSpanProcessor</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>四站 Web 在 trace 匯出前遮蔽 email、電話、地址、token，並將 LINE UID 雜湊化。</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>只治理 observability 出站資料；不代替 API 回應遮蔽、資料庫加密或 GDPR 刪除。</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>PLT·OBS</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（instrumentation 已實作；集中 collector/IaC 缺）</t>
+        </is>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §8.2、§9</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §12</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>web/{brand-portal,tech-portal,landing,platform-console}/src/{instrumentation.ts,observability/piiScrub.ts}; agent/lockcore/observability/; knowledge-pipeline/refinery/refinery/observability.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>Flow DSL executor</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>讀取 Vertical Pack 的宣告式 flow，驗 guard、執行 block、持久化狀態/事件並掛 SLA timer。</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>只執行可驗證 DSL；拒絕任意 inline code，也不把 UI 編輯器當執行後端。</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="inlineStr">
+        <is>
+          <t>API·WO、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>domain blocks / primitives</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>雙層工單積木：對外是派工/報價/收款等粗顆粒 block，內部由查資料、轉狀態、發事件等 primitive 組合。</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>每顆積木必須有 inputs/preconditions/guards/effects 契約；不允許無法靜態驗證的自由腳本。</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>API·WO、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>AS-BUILT ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §4.2、§9 ｜ 12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>api/services/{work_order_service,consent_service}.py; api/routers/work_orders_v2.py; api/core/db.py ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>Vertical Pack</t>
+        </is>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C100" s="13" t="inlineStr">
+        <is>
+          <t>可版本化的產業設定包，組合 field metadata、flow、catalog、knowledge、UI composition 與 blocks。</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="inlineStr">
+        <is>
+          <t>承載產業/品牌差異；不改寫身分、金流、事件等平台不變核心。</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="inlineStr">
+        <is>
+          <t>PLT·CFG、PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成） ｜ TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G100" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10 ｜ 15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作） ｜ 待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>FlowEditor</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>對 flow DSL 進行拖拉或表單編輯的薄 UI，輸出仍是可版控、可驗證的 DSL。</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>不直接執行任意程式；金流、派工與同意書仍受保護層及人工審核 gate。</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>PLT·FLOW</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>TO-BE（M4 設計）</t>
+        </is>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §2.1、§3.2–3.7、§10</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>待 M4 實作；目前為 SDS 設計元件</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="36" customHeight="1">
+      <c r="A102" s="13" t="inlineStr">
+        <is>
+          <t>Agent Configuration Studio / Config Registry</t>
+        </is>
+      </c>
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C102" s="13" t="inlineStr">
+        <is>
+          <t>管理 skill、RAG 權限、prompt、品牌設定與版本/分階段發布的中央設定能力。</t>
+        </is>
+      </c>
+      <c r="D102" s="13" t="inlineStr">
+        <is>
+          <t>租戶只可改客製層；安全、金額、工具允許清單等保護層不可 override。</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>M18 Config Registry</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>已實作的設定服務與路由，管理受控 namespace、版本、canary 與回復流程。</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>只涵蓋現行 M18 設定能力；不等於完整 FlowEditor 或跨產業 Studio 已完成。</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>Skill Revision Registry</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>以 skill_revisions 保存品牌 skill draft/published 版本，供 SkillSync 取得已發布內容。</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>版本庫不自行核准內容；發布權限、保護層與稽核仍由 API/後台治理。</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="inlineStr">
+        <is>
+          <t>PLT·CFG</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
           <t>HITL 審核骨架</t>
         </is>
       </c>
-      <c r="B78" s="13" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C78" s="13" t="inlineStr">
+      <c r="C105" s="11" t="inlineStr">
         <is>
           <t>共用的 draft→diff→人工審核→核可/駁回→發布模式，同時支援知識精煉與 AI Onboarding Compiler。</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D105" s="11" t="inlineStr">
         <is>
           <t>AI 只產生 draft；高風險知識或流程未人工審核不得實作。</t>
         </is>
       </c>
-      <c r="E78" s="13" t="inlineStr">
+      <c r="E105" s="11" t="inlineStr">
         <is>
           <t>PLT·CFG</t>
         </is>
       </c>
-      <c r="F78" s="14" t="inlineStr">
-        <is>
-          <t>12_SAD §9 L396, L398, L400</t>
-        </is>
-      </c>
-      <c r="G78" s="14" t="inlineStr">
-        <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
-        </is>
-      </c>
-      <c r="H78" s="13" t="inlineStr">
-        <is>
-          <t>待 M4/M5 實作；目前為 SAD/ADR/SDS 設計元件</t>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>PARTIAL（M18/LiveSkill 已實作；完整 Studio 未完成）</t>
+        </is>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>12_SAD §9</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="inlineStr">
+        <is>
+          <t>15_SDS §3.2、§10、§13</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>api/services/config_m18_service.py; api/routers/{config_m18,internal_skills}.py; web/brand-portal/src/components/knowledge-base/（部分實作）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H78"/>
+  <autoFilter ref="A4:I105"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H78">
+  <conditionalFormatting sqref="A5:I105">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("🔴",A5))</formula>
     </cfRule>
@@ -13756,154 +15401,208 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F78" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId202"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -14035,7 +15734,7 @@
       </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>當客戶傳送文字或照片時，合法訊息會進入客服流程並收到回覆；無效來源被拒絕，系統異常時仍有友善說明。</t>
+          <t>當客戶傳送文字或照片時，合法訊息會進入客服流程並收到回覆；Chatlock 安裝前拍照引導可附核准樣本圖，其他品牌維持純文字；無效來源被拒絕，系統異常時仍有友善說明。</t>
         </is>
       </c>
       <c r="G2" s="11" t="inlineStr">
@@ -14065,17 +15764,17 @@
       </c>
       <c r="L2" s="11" t="inlineStr">
         <is>
-          <t>line_gateway; AgentLoop; AgentRunner</t>
+          <t>line_gateway; Photo Guide resolver; Quote postback message mapper; WebhookIdempotencyStore; AgentLoop; AgentRunner</t>
         </is>
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L138–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -14137,17 +15836,17 @@
       </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
-          <t>line_gateway; AgentLoop; AgentRunner</t>
+          <t>line_gateway; Photo Guide resolver; Quote postback message mapper; WebhookIdempotencyStore; AgentLoop; AgentRunner</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L138–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -14179,7 +15878,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>當問題卡資訊完整時，客戶會先收到相符的解決建議並被詢問是否已釐清；連續三次未釐清時自動轉人工。</t>
+          <t>當問題資訊不足時，系統依當下情境一次列齊必要問題；客戶明確要求真人、急迫派工、涉及金錢或連續兩次表達不滿時立即轉人工，不採固定追問輪數。</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
@@ -14209,17 +15908,17 @@
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="M4" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -14281,17 +15980,17 @@
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -14353,17 +16052,17 @@
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -14425,17 +16124,17 @@
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; 記憶 DB</t>
+          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; SkillSync; 記憶 DB</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
+          <t>15_SDS §5.1</t>
         </is>
       </c>
     </row>
@@ -14497,17 +16196,17 @@
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; 記憶 DB</t>
+          <t>ContextBuilder; MemoryManager + Store; SkillsLoader + 2 builtin skills; SkillSync; 記憶 DB</t>
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L147–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="N8" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L368, L372–374</t>
+          <t>15_SDS §5.1</t>
         </is>
       </c>
     </row>
@@ -14574,12 +16273,12 @@
       </c>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L369–374; §5.4</t>
+          <t>15_SDS §5.1、§5.4</t>
         </is>
       </c>
     </row>
@@ -14641,17 +16340,17 @@
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>AgentLoop; AgentRunner; ToolRegistry; EscalationStore</t>
+          <t>AgentLoop; AgentRunner; ReplyGuard; SentimentClassifier; ToolRegistry; EscalationStore</t>
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="N10" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L367–374; §5.3</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -14713,17 +16412,17 @@
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>line_gateway; AgentLoop; AgentRunner</t>
+          <t>line_gateway; Photo Guide resolver; Quote postback message mapper; WebhookIdempotencyStore; AgentLoop; AgentRunner</t>
         </is>
       </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L138–149</t>
+          <t>12_SAD §4.1</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L358–374</t>
+          <t>15_SDS §5.1、§5.3</t>
         </is>
       </c>
     </row>
@@ -14790,12 +16489,12 @@
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L145–148; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="N12" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L369–374; §5.4</t>
+          <t>15_SDS §5.1、§5.4</t>
         </is>
       </c>
     </row>
@@ -14966,7 +16665,7 @@
       </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>AI 可草擬問題卡，客服能補齊與確認；未達完整度或未經客服確認時，不得自動轉成工單。</t>
+          <t>AI 可草擬問題卡，並將同一對話近 24 小時內最多 5 張客戶照片附上供客服檢視；客服能補齊與確認，未達完整度或未經客服確認時不得自動轉成工單。</t>
         </is>
       </c>
       <c r="G2" s="11" t="inlineStr">
@@ -14996,17 +16695,17 @@
       </c>
       <c r="L2" s="11" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
     </row>
@@ -15038,7 +16737,7 @@
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>報價必須依序完成內部核准、客戶送達與客戶確認；保固或專案報價不得由 AI 直接送出，客戶畫面不顯示成本欄位。</t>
+          <t>報價必須依序完成內部核准、客戶送達與客戶確認；重複同一決定安全回放，相反決定、過期、無權或找不到報價時顯示對應說明；保固或專案報價不得由 AI 直接送出，客戶畫面不顯示成本欄位。</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
@@ -15068,17 +16767,17 @@
       </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
     </row>
@@ -15140,17 +16839,17 @@
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="M4" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
     </row>
@@ -15182,7 +16881,7 @@
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>報價已獲客戶確認或符合急件例外時，客服可一次操作建立工單；重複送出不產生第二張工單，並留下建單來源。</t>
+          <t>報價已獲客戶確認或符合急件例外時，客服可一次操作建立工單；問題卡中的客戶姓名、電話、地址、品牌、型號與序號會帶入工單，重複送出不產生第二張工單並留下建單來源。</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
@@ -15212,17 +16911,17 @@
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）; Flow DSL executor; domain blocks / primitives; core/db.py</t>
+          <t>Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; core/db.py</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
     </row>
@@ -15284,17 +16983,17 @@
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）; Redis pub/sub; Kafka; 分散式排程</t>
+          <t>Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程</t>
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
     </row>
@@ -15356,17 +17055,17 @@
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）; Redis pub/sub; Kafka; 分散式排程</t>
+          <t>Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
     </row>
@@ -15428,17 +17127,17 @@
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>Service Layer（dispatch）; Redis pub/sub; Kafka; 分散式排程</t>
+          <t>Service Layer（dispatch）; dispatch_service candidate scoring; Redis pub/sub; Kafka; PG Advisory Cron Leader; 分散式排程</t>
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §8.1–8.2 L353–372</t>
+          <t>12_SAD §4.2、§8</t>
         </is>
       </c>
       <c r="N8" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L444–466; §6.3 L484–492; §11.1 L648–660</t>
+          <t>15_SDS §6.1、§6.3、§11.1</t>
         </is>
       </c>
     </row>
@@ -15470,7 +17169,7 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>技師可上傳到場與施工證據、登錄受控材料並取得客戶簽名；證據不齊或現場範圍變更未完成必要確認時不得結案。</t>
+          <t>技師可上傳到場與施工證據、登錄受控材料；客服可將三段免責簽署連結推送到 LINE，未綁 LINE 時可複製連結交付；證據、簽署或現場範圍變更確認不齊時不得結案。</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -15500,17 +17199,17 @@
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）; Flow DSL executor; domain blocks / primitives; core/db.py</t>
+          <t>Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; core/db.py</t>
         </is>
       </c>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
     </row>
@@ -15572,17 +17271,17 @@
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>Service Layer（work_order）; Flow DSL executor; domain blocks / primitives; core/db.py</t>
+          <t>Service Layer（work_order）; Consent link service; Flow DSL executor; domain blocks / primitives; core/db.py</t>
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L397</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="N10" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §3.3–3.5 L144–188; §4.1–4.2 L209–252; §6.1 L444–466</t>
+          <t>15_SDS §3.3–3.5、§4.1–4.2、§6.1</t>
         </is>
       </c>
     </row>
@@ -15649,12 +17348,12 @@
       </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
     </row>
@@ -15721,12 +17420,12 @@
       </c>
       <c r="M12" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="N12" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
     </row>
@@ -15793,12 +17492,12 @@
       </c>
       <c r="M13" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L401</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L250–252; §6.1 L444–466; §7.3 L554–560</t>
+          <t>15_SDS §4.2、§6.1、§7.3</t>
         </is>
       </c>
     </row>
@@ -15860,17 +17559,17 @@
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; Kafka; line_push_service + outbox worker</t>
+          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; EventBusProducer; Kafka; line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="N14" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
     </row>
@@ -15932,17 +17631,17 @@
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; Kafka; line_push_service + outbox worker</t>
+          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; EventBusProducer; Kafka; line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="M15" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
     </row>
@@ -16004,17 +17703,17 @@
       </c>
       <c r="L16" s="11" t="inlineStr">
         <is>
-          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; Kafka; line_push_service + outbox worker</t>
+          <t>internal_ingest.py; WebSocket 端點; Redis pub/sub; EventBusProducer; Kafka; line_push_service + outbox worker</t>
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="N16" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L432–466; §6.2–6.3 L474–492; §11 L648–677</t>
+          <t>15_SDS §6.1–6.3、§11</t>
         </is>
       </c>
     </row>
@@ -16076,17 +17775,17 @@
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="M17" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
     </row>
@@ -16148,17 +17847,17 @@
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
     </row>
@@ -16220,17 +17919,17 @@
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
+          <t>API_SURFACE router filter; Three-DB Connection Router; DBPoolScopeMiddleware; DEKService + PII blind index + purge ledger; 守衛鏈; core/errors.py; core/idempotency.py; Middleware</t>
         </is>
       </c>
       <c r="M19" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164; §9 L393</t>
+          <t>12_SAD §4.2、§9</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L428–472; §6.4 L494–499</t>
+          <t>15_SDS §6.1、§6.4</t>
         </is>
       </c>
     </row>
@@ -16292,17 +17991,17 @@
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>tenant-scoped routers; Service Layer（problem_card / quote）; core/db.py</t>
+          <t>tenant-scoped routers; Service Layer（problem_card / quote）; Conversation media collector; core/db.py</t>
         </is>
       </c>
       <c r="M20" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L151–164</t>
+          <t>12_SAD §4.2</t>
         </is>
       </c>
       <c r="N20" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.2 L225–252; §4.6 L292–354; §6.1 L422–472</t>
+          <t>15_SDS §4.2、§4.6、§6.1</t>
         </is>
       </c>
     </row>
@@ -16524,12 +18223,12 @@
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
     </row>
@@ -16596,12 +18295,12 @@
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
     </row>
@@ -16633,7 +18332,7 @@
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>派工人員可查看工單看板、待派佇列與即時更新；即時連線中斷時畫面不崩潰，仍可查詢與完成核心作業。</t>
+          <t>派工人員可查看工單看板、待派佇列、技師全名與需授權照片的縮圖/放大檢視；即時連線中斷或照片載入失敗時畫面不崩潰，仍可查詢與完成核心作業。</t>
         </is>
       </c>
       <c r="G4" s="11" t="inlineStr">
@@ -16663,17 +18362,17 @@
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="M4" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
     </row>
@@ -16735,17 +18434,17 @@
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
     </row>
@@ -16812,12 +18511,12 @@
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L570–578</t>
+          <t>15_SDS §8.1</t>
         </is>
       </c>
     </row>
@@ -16849,7 +18548,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>客戶可查看報價明細、分層閱讀條款、勾選同意並追蹤工單進度；簡化備援方式也會準確記錄客戶同意來源。</t>
+          <t>客戶可由 LINE 或備援連結查看報價與三段免責條款、勾選同意並追蹤工單進度；公開 token 僅保存雜湊稽核，畫面遮蔽不必要個資。</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -16879,17 +18578,17 @@
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>api client; cache; realtime</t>
+          <t>api client; cache; realtime; AuthImage / AuthImageLightbox; ConsentPanel</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L575–578; §8.3 L593–599</t>
+          <t>15_SDS §8.1、§8.3</t>
         </is>
       </c>
     </row>
@@ -16921,7 +18620,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>任一主要 API、網路或頁面錯誤都顯示可理解的狀態、影響與下一步建議；錯誤不導致整個應用程式崩潰。</t>
+          <t>任一主要 API、網路、頁面或需認證媒體載入錯誤都顯示可理解的狀態、影響與下一步建議；錯誤不導致整個應用程式崩潰。</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -16956,12 +18655,12 @@
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.3 L166–177</t>
+          <t>12_SAD §4.3</t>
         </is>
       </c>
       <c r="N8" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §8.1 L564–578; §8.2–8.3 L580–599</t>
+          <t>15_SDS §8.1–8.3</t>
         </is>
       </c>
     </row>
@@ -17159,12 +18858,12 @@
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.6 L199–208</t>
+          <t>12_SAD §4.6</t>
         </is>
       </c>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L611–613; 附錄 L736</t>
+          <t>15_SDS §9.1；附錄</t>
         </is>
       </c>
     </row>
@@ -17226,17 +18925,17 @@
       </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; forward-only migrations; platform schema; core/db.py</t>
+          <t>SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
     </row>
@@ -17298,17 +18997,17 @@
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>SQL/Schema*.sql; forward-only migrations; platform schema; core/db.py</t>
+          <t>SQL/Schema*.sql; forward-only migrations; platform schema; Tech DB router + mirror; core/db.py</t>
         </is>
       </c>
       <c r="M4" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L160–162; §4.6 L207–208</t>
+          <t>12_SAD §4.2、§4.6</t>
         </is>
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §3.1 L81–124; §6.1 L448–451</t>
+          <t>15_SDS §3.1、§6.1</t>
         </is>
       </c>
     </row>
@@ -17375,12 +19074,12 @@
       </c>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §8.1 L353–361; §9 L407</t>
+          <t>12_SAD §5、§8–9</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §5.1 L376; §9.1 L617–619; §11.3 L677</t>
+          <t>15_SDS §5.1、§9.1、§11.3</t>
         </is>
       </c>
     </row>
@@ -17447,12 +19146,12 @@
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
     </row>
@@ -17519,12 +19218,12 @@
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §4.6 L199–208; §8.2 L372</t>
+          <t>12_SAD §4.2、§4.6、§8.2</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.3–6.4 L484–499; §9.3 L631–635; §11 L648–677</t>
+          <t>15_SDS §6.3–6.4、§9.3、§11</t>
         </is>
       </c>
     </row>
@@ -17720,12 +19419,12 @@
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L179–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L603–613; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
     </row>
@@ -17792,12 +19491,12 @@
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L614–615; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
     </row>
@@ -17859,17 +19558,17 @@
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>Draft Queue; 審核 UI backend</t>
+          <t>Draft Queue; 審核 UI backend; Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="M4" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L615–616; §9.2 L621–629</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
     </row>
@@ -17931,17 +19630,17 @@
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>Publisher; 品牌庫 pgvector; SkillsLoader + 2 builtin skills</t>
+          <t>Publisher; behavior patch artifact; LiveSkill DB ingest; 品牌庫 pgvector; SkillsLoader + 2 builtin skills</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L617–619; §9.3 L631–635</t>
+          <t>15_SDS §9.1、§9.3</t>
         </is>
       </c>
     </row>
@@ -18003,17 +19702,17 @@
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>Draft Queue; 審核 UI backend</t>
+          <t>Draft Queue; 審核 UI backend; Casdoor reviewer auth</t>
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.4 L183–187</t>
+          <t>12_SAD §4.4</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §9.1 L615–616; §9.2 L621–629</t>
+          <t>15_SDS §9.1–9.2</t>
         </is>
       </c>
     </row>
@@ -18202,17 +19901,17 @@
       </c>
       <c r="L2" s="11" t="inlineStr">
         <is>
-          <t>self-service routers; 守衛鏈; technician_service; certification/kyc_service; lock_tech</t>
+          <t>API_SURFACE router filter; self-service routers; 守衛鏈; technician_service; certification/kyc_service; Tech DB router + mirror; lock_tech</t>
         </is>
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18274,17 +19973,17 @@
       </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
-          <t>self-service routers; 守衛鏈; technician_service; certification/kyc_service; lock_tech</t>
+          <t>API_SURFACE router filter; self-service routers; 守衛鏈; technician_service; certification/kyc_service; Tech DB router + mirror; lock_tech</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18346,17 +20045,17 @@
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>OHS API routers; matching_service; schedule_service; WebSocket 端點; 事件層</t>
+          <t>OHS API routers; dispatch_service candidate scoring; schedule_service; WebSocket 端點; 事件層</t>
         </is>
       </c>
       <c r="M4" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18418,17 +20117,17 @@
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>OHS API routers; matching_service; schedule_service; WebSocket 端點; 事件層</t>
+          <t>OHS API routers; dispatch_service candidate scoring; schedule_service; WebSocket 端點; 事件層</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18490,17 +20189,17 @@
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>事件層; 技師工單 read-model; WebSocket 端點</t>
+          <t>事件層; EventConsumerWorker; technician_workorder_projection; 技師工單 read-model; WebSocket 端點</t>
         </is>
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L193–197; §8.2 L369, L372</t>
+          <t>12_SAD §4.5、§8.2</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L513–518; §7.3 L554–560; §11.1 L648–660</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
     </row>
@@ -18562,17 +20261,17 @@
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>commission_settlement_service; 技師工單 read-model; Kafka</t>
+          <t>technician settlement services; technician_commission_projection; EventConsumerWorker; Kafka</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197; §9 L401</t>
+          <t>12_SAD §4.5、§9</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L515–518; §7.3 L554–560; §11.1 L648–660</t>
+          <t>15_SDS §7.1、§7.3、§11.1</t>
         </is>
       </c>
     </row>
@@ -18634,17 +20333,17 @@
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>OHS API routers; matching_service; schedule_service; WebSocket 端點; 事件層</t>
+          <t>OHS API routers; dispatch_service candidate scoring; schedule_service; WebSocket 端點; 事件層</t>
         </is>
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="N8" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §4.4 L258–279; §7.1 L503–518; §7.2 L522–548</t>
+          <t>15_SDS §4.4、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18706,17 +20405,17 @@
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>self-service routers; 守衛鏈; technician_service; certification/kyc_service; lock_tech</t>
+          <t>API_SURFACE router filter; self-service routers; 守衛鏈; technician_service; certification/kyc_service; Tech DB router + mirror; lock_tech</t>
         </is>
       </c>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.5 L189–197</t>
+          <t>12_SAD §4.2、§4.5</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §7.1 L503–518; §7.2 L550–552</t>
+          <t>15_SDS §6.1、§7.1–7.2</t>
         </is>
       </c>
     </row>
@@ -18911,17 +20610,17 @@
       </c>
       <c r="L2" s="11" t="inlineStr">
         <is>
-          <t>Casdoor; 平台維運 console; 守衛鏈; License provisioning</t>
+          <t>Casdoor; 平台維運 console; 守衛鏈; License Entitlement Gate; License provisioning</t>
         </is>
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
     </row>
@@ -18983,17 +20682,17 @@
       </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
-          <t>Casdoor; 平台維運 console; 守衛鏈; License provisioning</t>
+          <t>Casdoor; 平台維運 console; 守衛鏈; License Entitlement Gate; License provisioning</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
     </row>
@@ -19055,17 +20754,17 @@
       </c>
       <c r="L4" s="11" t="inlineStr">
         <is>
-          <t>Casdoor; 平台維運 console; 守衛鏈; License provisioning</t>
+          <t>Casdoor; 平台維運 console; 守衛鏈; License Entitlement Gate; License provisioning</t>
         </is>
       </c>
       <c r="M4" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §8.2–8.3 L363–376; §9 L390, L393</t>
+          <t>12_SAD §8.2–8.3、§9</t>
         </is>
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L40–56; §6.1 L437–442; §11.2 L662–670</t>
+          <t>15_SDS §2.1、§6.1、§11.2</t>
         </is>
       </c>
     </row>
@@ -19132,12 +20831,12 @@
       </c>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §4.2 L164; §8.1–8.2 L353–372; §9 L394</t>
+          <t>12_SAD §4.2、§8–9</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §6.1 L453–466; §6.3 L484–492; §11 L648–677</t>
+          <t>15_SDS §6.1、§6.3、§11</t>
         </is>
       </c>
     </row>
@@ -19204,12 +20903,12 @@
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §4.1 L146; §9 L395, L407</t>
+          <t>12_SAD §4.1、§9</t>
         </is>
       </c>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.2 L68; §5.1 L370; §13 L707</t>
+          <t>15_SDS §2.2、§5.1、§13</t>
         </is>
       </c>
     </row>
@@ -19271,17 +20970,17 @@
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>SigNoz; OPIK; OpenTelemetry</t>
+          <t>SigNoz; OPIK; OpenTelemetry; PIIScrubSpanProcessor</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §8.2 L363–372; §9 L389</t>
+          <t>12_SAD §8.2、§9</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §12 L681–696（韌性與觀測證據使用面）</t>
+          <t>15_SDS §12</t>
         </is>
       </c>
     </row>
@@ -19348,12 +21047,12 @@
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396–398</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="N8" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §2.1 L36–59; §3.2–3.7 L126–205; §10 L639–644</t>
+          <t>15_SDS §2.1、§3.2–3.7、§10</t>
         </is>
       </c>
     </row>
@@ -19415,17 +21114,17 @@
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry; Vertical Pack; HITL 審核骨架</t>
+          <t>Agent Configuration Studio / Config Registry; M18 Config Registry; Skill Revision Registry; Vertical Pack; HITL 審核骨架</t>
         </is>
       </c>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396, L398, L400</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
+          <t>15_SDS §3.2、§10、§13</t>
         </is>
       </c>
     </row>
@@ -19487,17 +21186,17 @@
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>Agent Configuration Studio / Config Registry; Vertical Pack; HITL 審核骨架</t>
+          <t>Agent Configuration Studio / Config Registry; M18 Config Registry; Skill Revision Registry; Vertical Pack; HITL 審核骨架</t>
         </is>
       </c>
       <c r="M10" s="12" t="inlineStr">
         <is>
-          <t>12_SAD §9 L396, L398, L400</t>
+          <t>12_SAD §9</t>
         </is>
       </c>
       <c r="N10" s="12" t="inlineStr">
         <is>
-          <t>15_SDS §3.2 L126–142; §10 L639–644; §13 L704–709</t>
+          <t>15_SDS §3.2、§10、§13</t>
         </is>
       </c>
     </row>
@@ -19674,7 +21373,7 @@
       </c>
       <c r="H2" s="11" t="inlineStr">
         <is>
-          <t>驗證方式：k6 50 位並行使用者、15 分鐘穩定負載；輸出 p95/p99、錯誤率與逾時分布</t>
+          <t>驗證方式：k6 load 50 位並行使用者（實測 [待確認]） 上游含 [待確認]，需先定量測環境/關卡。</t>
         </is>
       </c>
       <c r="I2" s="11" t="inlineStr">
@@ -19684,7 +21383,7 @@
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
-          <t>✅ 營運目標</t>
+          <t>❓ 待確認</t>
         </is>
       </c>
       <c r="K2" s="11" t="inlineStr">
@@ -19957,12 +21656,12 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>p95 &lt; 300ms；50 位並行使用者、15 分鐘穩定負載，錯誤率 &lt; 1%</t>
+          <t>p95 &lt; 300ms（設計目標；實測 [待確認]）</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>驗證方式：k6 + APM（SigNoz），依端點輸出 latency/error 分布</t>
+          <t>驗證方式：APM（SigNoz） 上游含 [待確認]，需先定量測環境/關卡。</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
@@ -19972,7 +21671,7 @@
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>✅ 營運目標</t>
+          <t>❓ 待確認</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
@@ -20101,12 +21800,12 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>p95 &lt; 300ms；10,000 筆技師基準資料、50 位並行使用者、15 分鐘穩定負載，錯誤率 &lt; 1%</t>
+          <t>p95 &lt; 300ms（設計目標；實測 [待確認]）</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>驗證方式：k6 + read replica 路由驗證；保存資料集版本與查詢計畫</t>
+          <t>驗證方式：k6 + read replica 路由驗證上游含 [待確認]，需先定量測環境/關卡。</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
@@ -20116,7 +21815,7 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>✅ 營運目標</t>
+          <t>❓ 待確認</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
@@ -20389,12 +22088,12 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>≤ 3s；Lighthouse mobile / Fast 4G / 4× CPU slowdown，5 次測試中位數</t>
+          <t>≤ 3s [待確認]</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>驗證方式：Lighthouse CI + RUM P75 交叉驗證</t>
+          <t>驗證方式：Lighthouse / RUM 上游含 [待確認]，需先定量測環境/關卡。</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -20404,7 +22103,7 @@
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>✅ 營運目標</t>
+          <t>❓ 待確認</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
@@ -942,17 +942,15 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>6/7 有案例</t>
+          <t>7/7 有案例</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>S1：6 案例</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>4</v>
-      </c>
+          <t>S1：13 案例</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr"/>
       <c r="O2" s="6" t="inlineStr"/>
       <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="6" t="inlineStr"/>
@@ -1012,17 +1010,15 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>6/7 有案例</t>
+          <t>7/7 有案例</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>S1：7 案例</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v>4</v>
-      </c>
+          <t>S1：12 案例</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr"/>
       <c r="O3" s="6" t="inlineStr"/>
       <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
@@ -1082,17 +1078,15 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>5/6 有案例</t>
+          <t>6/6 有案例</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>S1：4 案例</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>S1：6 案例</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="6" t="inlineStr"/>
       <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="6" t="inlineStr"/>
@@ -1157,12 +1151,10 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>S2：11 案例</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>S2：12 案例</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr"/>
       <c r="O5" s="6" t="inlineStr"/>
       <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="6" t="inlineStr"/>
@@ -1222,17 +1214,15 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>5/7 有案例</t>
+          <t>7/7 有案例</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>S2：6 案例</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>S2：12 案例</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="6" t="inlineStr"/>
       <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="6" t="inlineStr"/>
@@ -1292,17 +1282,15 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>5/6 有案例</t>
+          <t>6/6 有案例</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>S2：9 案例</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>5</v>
-      </c>
+          <t>S2：15 案例</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr"/>
       <c r="O7" s="6" t="inlineStr"/>
       <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="6" t="inlineStr"/>
@@ -1367,12 +1355,10 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>S2：5 案例</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>4</v>
-      </c>
+          <t>S2：7 案例</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr"/>
       <c r="O8" s="6" t="inlineStr"/>
       <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="6" t="inlineStr"/>
@@ -1437,12 +1423,10 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>S4：8 案例</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>S4：11 案例</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr"/>
       <c r="O9" s="6" t="inlineStr"/>
       <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="6" t="inlineStr"/>
@@ -1507,12 +1491,10 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>1 案例</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>4 案例</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr"/>
       <c r="O10" s="6" t="inlineStr"/>
       <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="6" t="inlineStr"/>
@@ -1577,12 +1559,10 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>⚠ 無驗收腳本</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>S6：5 案例</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr"/>
       <c r="O11" s="6" t="inlineStr"/>
       <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="6" t="inlineStr"/>
@@ -1647,12 +1627,10 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>S4：2 案例</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>3</v>
-      </c>
+          <t>S4：5 案例</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr"/>
       <c r="O12" s="6" t="inlineStr"/>
       <c r="P12" s="6" t="inlineStr"/>
       <c r="Q12" s="6" t="inlineStr"/>
@@ -1712,17 +1690,15 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2/4 有案例</t>
+          <t>4/4 有案例</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>⚠ 無驗收腳本</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>S7：6 案例</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr"/>
       <c r="O13" s="6" t="inlineStr"/>
       <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="6" t="inlineStr"/>
@@ -1787,12 +1763,10 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>1 案例</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>3 案例</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr"/>
       <c r="O14" s="6" t="inlineStr"/>
       <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="6" t="inlineStr"/>
@@ -1852,17 +1826,15 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>3/4 有案例</t>
+          <t>4/4 有案例</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>⚠ 無驗收腳本</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>S8：6 案例</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr"/>
       <c r="O15" s="6" t="inlineStr"/>
       <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="6" t="inlineStr"/>
@@ -1922,17 +1894,15 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>4/9 有案例</t>
+          <t>9/9 有案例</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>S3：1 案例</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>S3：6 案例</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr"/>
       <c r="O16" s="6" t="inlineStr"/>
       <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr"/>
@@ -1997,12 +1967,10 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>S3：1 案例</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>S3：3 案例</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr"/>
       <c r="O17" s="6" t="inlineStr"/>
       <c r="P17" s="6" t="inlineStr"/>
       <c r="Q17" s="6" t="inlineStr"/>
@@ -2062,17 +2030,15 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2/4 有案例</t>
+          <t>4/4 有案例</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>⚠ 無驗收腳本</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>1</v>
-      </c>
+          <t>S9：6 案例</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr"/>
       <c r="O18" s="6" t="inlineStr"/>
       <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="6" t="inlineStr"/>
@@ -2132,17 +2098,15 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>1/4 有案例</t>
+          <t>4/4 有案例</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>S5：1 案例</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>S5：6 案例</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr"/>
       <c r="O19" s="6" t="inlineStr"/>
       <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="6" t="inlineStr"/>
@@ -2207,12 +2171,10 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>S4：5 案例</t>
-        </is>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v>2</v>
-      </c>
+          <t>S4：7 案例</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr"/>
       <c r="O20" s="6" t="inlineStr"/>
       <c r="P20" s="6" t="inlineStr"/>
       <c r="Q20" s="6" t="inlineStr"/>
@@ -2381,7 +2343,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -2428,7 +2390,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>happy、boundary</t>
+          <t>happy、boundary、recovery</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -2475,7 +2437,7 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -2569,7 +2531,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -2616,7 +2578,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -2663,7 +2625,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -2710,7 +2672,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2804,7 +2766,7 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2851,7 +2813,7 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2898,7 +2860,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2992,7 +2954,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>happy、boundary</t>
+          <t>happy、boundary、recovery</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -3133,7 +3095,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -3180,7 +3142,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -3227,7 +3189,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -3274,7 +3236,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -3368,7 +3330,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、recovery</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -3556,7 +3518,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -3603,7 +3565,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -3979,7 +3941,7 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -4167,7 +4129,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -4214,7 +4176,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -4261,7 +4223,7 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -4355,7 +4317,7 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -4496,7 +4458,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -4543,7 +4505,7 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -4590,7 +4552,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -4825,7 +4787,7 @@
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -4872,7 +4834,7 @@
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -5295,7 +5257,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -5483,7 +5445,7 @@
       </c>
       <c r="H69" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
@@ -5671,7 +5633,7 @@
       </c>
       <c r="H73" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -5718,7 +5680,7 @@
       </c>
       <c r="H74" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
@@ -5859,7 +5821,7 @@
       </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
@@ -5953,7 +5915,7 @@
       </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -6047,7 +6009,7 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
@@ -6094,7 +6056,7 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -6188,7 +6150,7 @@
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
@@ -6235,7 +6197,7 @@
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
@@ -6282,7 +6244,7 @@
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
@@ -6423,7 +6385,7 @@
       </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
@@ -6564,7 +6526,7 @@
       </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
@@ -6658,7 +6620,7 @@
       </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr">
@@ -6799,7 +6761,7 @@
       </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
@@ -6846,7 +6808,7 @@
       </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
@@ -6893,7 +6855,7 @@
       </c>
       <c r="H99" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
@@ -6940,7 +6902,7 @@
       </c>
       <c r="H100" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
@@ -6987,7 +6949,7 @@
       </c>
       <c r="H101" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I101" s="5" t="inlineStr">
@@ -7034,7 +6996,7 @@
       </c>
       <c r="H102" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
@@ -7081,7 +7043,7 @@
       </c>
       <c r="H103" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I103" s="5" t="inlineStr">
@@ -7128,7 +7090,7 @@
       </c>
       <c r="H104" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I104" s="5" t="inlineStr">
@@ -7175,7 +7137,7 @@
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
@@ -7222,7 +7184,7 @@
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I106" s="5" t="inlineStr">
@@ -7269,7 +7231,7 @@
       </c>
       <c r="H107" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I107" s="5" t="inlineStr">
@@ -7316,7 +7278,7 @@
       </c>
       <c r="H108" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
@@ -7363,7 +7325,7 @@
       </c>
       <c r="H109" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I109" s="5" t="inlineStr">
@@ -7410,7 +7372,7 @@
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I110" s="5" t="inlineStr">
@@ -7457,7 +7419,7 @@
       </c>
       <c r="H111" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I111" s="5" t="inlineStr">
@@ -7504,7 +7466,7 @@
       </c>
       <c r="H112" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I112" s="5" t="inlineStr">
@@ -7551,7 +7513,7 @@
       </c>
       <c r="H113" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I113" s="5" t="inlineStr">
@@ -7598,7 +7560,7 @@
       </c>
       <c r="H114" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I114" s="5" t="inlineStr">
@@ -7645,7 +7607,7 @@
       </c>
       <c r="H115" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I115" s="5" t="inlineStr">
@@ -7692,7 +7654,7 @@
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I116" s="5" t="inlineStr">
@@ -7739,7 +7701,7 @@
       </c>
       <c r="H117" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I117" s="5" t="inlineStr">
@@ -7786,7 +7748,7 @@
       </c>
       <c r="H118" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I118" s="5" t="inlineStr">
@@ -7833,7 +7795,7 @@
       </c>
       <c r="H119" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I119" s="5" t="inlineStr">
@@ -7927,7 +7889,7 @@
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
@@ -7974,7 +7936,7 @@
       </c>
       <c r="H122" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
@@ -8021,7 +7983,7 @@
       </c>
       <c r="H123" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -8068,7 +8030,7 @@
       </c>
       <c r="H124" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
@@ -8115,7 +8077,7 @@
       </c>
       <c r="H125" s="5" t="inlineStr">
         <is>
-          <t>無案例</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
@@ -8256,7 +8218,7 @@
       </c>
       <c r="H128" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>recovery</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr">
@@ -8303,7 +8265,7 @@
       </c>
       <c r="H129" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr">
@@ -8397,7 +8359,7 @@
       </c>
       <c r="H131" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>happy、failure</t>
         </is>
       </c>
       <c r="I131" s="5" t="inlineStr">
@@ -8444,7 +8406,7 @@
       </c>
       <c r="H132" s="5" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>failure</t>
         </is>
       </c>
       <c r="I132" s="5" t="inlineStr">

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
@@ -10,10 +10,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 旅程驗收主表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 旅程展開（SC × 需求）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 旅程 × Persona（誰在走）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ BDD 行為情境（生成）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 旅程驗收主表'!$A$1:$R$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 旅程展開（SC × 需求）'!$A$1:$I$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'④ 旅程 × Persona（誰在走）'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⑤ BDD 行為情境（生成）'!$A$1:$H$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8466,4 +8470,4008 @@
   <autoFilter ref="A1:I133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>旅程</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>分線</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Persona ID</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>這條旅程憑什麼由這個 Persona 感知</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SC-01</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>產品疑問自助解決（不建卡）</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>終端客戶</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>客戶在 LINE 自助解決產品疑問，旅程完全由客戶感知，不建卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SC-02</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>故障報修到問題卡成立</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>終端客戶</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>客戶描述故障、拍照，直到問題卡成立——客戶是唯一發起者</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>急件強制轉真人</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>終端客戶</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>被鎖在門外的急件客戶要求真人，情緒與時效由客戶端定義成敗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>報價確認到工單成立</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>終端客戶</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>客戶於 LIFF 查看報價明細並勾選同意——確認動作是旅程主軸</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>報價確認到工單成立</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-01</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>派工小編內部核准並 1-click 建立工單，是必要協作但非旅程主體</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>派工媒合到技師接單</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-01</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>派工小編（或自動媒合）發動派工，佇列清空是其成功定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>派工媒合到技師接單</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>簽約師傅</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>師傅接單使旅程完成，但派工決策端在小編/系統</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SC-06</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>現場施工到完工結案</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>簽約師傅</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>師傅到場施工、拍照存證、回報完工——現場旅程由師傅走完</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SC-06</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>現場施工到完工結案</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>終端客戶</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>客戶現場簽收確認，是完工 gate 的必要一方</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SC-07</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>現場範圍變更與報價修正</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>簽約師傅</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>師傅在現場發現範圍變更、發起 requote，變更由師傅端觸發</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SC-07</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>現場範圍變更與報價修正</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>終端客戶</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>客戶重新確認修正後報價，否則不得續作</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SC-08</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>收款、取消與退款</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>終端客戶</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>客戶付款、或發起取消/退款——金流動作由客戶感知</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SC-08</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>收款、取消與退款</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-01</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>小編處理取消費分層與退款覆寫，留稽核</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SC-09</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>月結與七帳本對帳</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-02</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>租戶 Admin（品牌管理者）</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>租戶 Admin 執行月結與七帳本對帳，borrow=lend 是其成功定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>SC-10</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>人工接管與對話不蒸發</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>L1-OPS</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>PER-OPS-01</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>小編人工接管對話，接管期間對話零缺漏是其成功定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>SC-11</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>例外審批與 SoD 收件匣</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>L1-OPS</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>PER-OPS-01</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>小編在例外收件匣處理 reschedule/dispute，日常操作者</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>SC-11</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>例外審批與 SoD 收件匣</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>L1-OPS</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>PER-OPS-02</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>租戶 Admin（品牌管理者）</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>敏感操作觸發 SoD 時由租戶 Admin 任二不同角色核准</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>SC-12</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>技師註冊、KYC 到品牌授權</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>PER-TEC-01</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>簽約師傅</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>師傅提交註冊與 KYC 材料，取得品牌授權是其旅程目標</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>SC-12</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>技師註冊、KYC 到品牌授權</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>PER-PLT-01</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>平台管理員（Super Admin）</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Super Admin 審核 KYC 與認證、開通品牌授權</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>SC-13</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>技師跨品牌對帳與佣金請領</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>PER-TEC-01</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>簽約師傅</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>師傅查跨品牌對帳單、請領佣金——單一 statement 對得起是成功定義</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>SC-14</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>認證撤銷與停權即時廣播</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>PER-PLT-01</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>平台管理員（Super Admin）</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Super Admin 撤銷認證/停權並即時廣播，跨租戶治理由平台端執行</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>知識精煉 HITL 到雙路發布</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>L1-KNW</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>PER-KNW-01</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>客服主管</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>客服主管發起知識精煉、判定是否進 HITL——精煉由營運端啟動</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>知識精煉 HITL 到雙路發布</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>L1-KNW</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>PER-KNW-02</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Domain Expert（領域專家）</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Domain Expert 審核事實正確性與 provenance，是發布前必要關卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>SC-16</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>SOP 雙審與 Family Reviewer 覆核</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>L1-KNW</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>PER-KNW-02</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Domain Expert（領域專家）</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Domain Expert 主審 SOP 內容，第一關由領域專家把關</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>SC-16</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>SOP 雙審與 Family Reviewer 覆核</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>L1-KNW</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>PER-KNW-03</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Family Reviewer（安全覆核者）</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Family Reviewer 做使用者視角安全覆核，高風險 SOP 第二關</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>SC-17</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>品牌申請到 License 開通上線</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>PER-PLT-02</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>潛在加盟品牌</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>潛在加盟品牌從 landing 提出申請，上線是申請者的旅程目標</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>SC-17</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>品牌申請到 License 開通上線</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>PER-PLT-01</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>平台管理員（Super Admin）</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Super Admin 審申請、開 License、觸發 provisioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>品牌自助配置與治理回滾</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>PER-OPS-02</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>租戶 Admin（品牌管理者）</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>租戶 Admin 自助配置品牌設定並在出錯時治理回滾</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>SC-19</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>GDPR 被遺忘權執行</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>PER-CUS-01</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>終端客戶</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>主要感知者</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>客戶（data subject）行使被遺忘權，請求由客戶端發起</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>SC-19</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>GDPR 被遺忘權執行</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>PER-PLT-03</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>DPO（資料保護官）</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>協作者</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>DPO 檢查 legal-hold、執行合規銷毀並留 append-only 稽核</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G31"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>旅程</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>分線</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>主要 Persona</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>情境類型</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Given（前置）</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>When（行為）</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Then（預期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>SC-01</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>產品疑問自助解決（不建卡）</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>客戶加官方帳號後，詢問一般產品操作或知識問題（如換電池、恢復原廠設定）</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>LINE 進線驗簽
+Turn 編排
+案例庫／知識檢索命中
+回答
+AI 主動確認「問題釐清了嗎」
+客戶確認
+對話結案</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>客戶問題被解答且未產生問題卡；回答內容與知識庫一致，無紅線違反</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>SC-01</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>產品疑問自助解決（不建卡）</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>客戶加官方帳號後，詢問一般產品操作或知識問題（如換電池、恢復原廠設定）</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>連續 3 次未釐清</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>自動升級轉真人（落入 SC-02）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SC-01</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>產品疑問自助解決（不建卡）</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>客戶加官方帳號後，詢問一般產品操作或知識問題（如換電池、恢復原廠設定）</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>詢價誘導</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>只給範圍價、不給確定金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SC-01</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>產品疑問自助解決（不建卡）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>客戶加官方帳號後，詢問一般產品操作或知識問題（如換電池、恢復原廠設定）</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>影像辨識請求</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>一律拒絕（僅存證）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>SC-02</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>故障報修到問題卡成立</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>客戶回報鎖具故障並要求派師傅</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>AI 追問品牌／型號／地址
+三層解決嘗試
+判定需人工
+transfer_to_human
+AI 草擬問題卡進後台
+客服補全
+completeness ≥ 0.85
+confirmed</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>問題卡狀態為 confirmed，欄位與對話事實一致，badge 標示 AI 草擬來源</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SC-02</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>故障報修到問題卡成立</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>客戶回報鎖具故障並要求派師傅</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>資料連 3 次收不齊</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>自動轉真人</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SC-02</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>故障報修到問題卡成立</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>客戶回報鎖具故障並要求派師傅</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>地址缺失</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>不擋建卡，延後到結案硬擋</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SC-02</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>故障報修到問題卡成立</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>客戶回報鎖具故障並要求派師傅</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>AI 承諾轉接卻未呼叫工具</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>gateway 兜底補一筆 escalation（案子不得蒸發）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>急件強制轉真人</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>進線內容命中急件四類——受困門外 / 受困室內 / 人身安全風險 / 怒客情緒</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Intent 階段判定急件
+bypass 三層解決
+5 分鐘內轉真人
+跳過報價直接建單
+4 小時內補稽核報價</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>urgency_detected_at 已寫入、TransferEvent 落檔、工單於 SLA 內成立</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>急件強制轉真人</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>進線內容命中急件四類——受困門外 / 受困室內 / 人身安全風險 / 怒客情緒</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>補稽核逾 4 小時</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>alert 升主管</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>急件強制轉真人</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>進線內容命中急件四類——受困門外 / 受困室內 / 人身安全風險 / 怒客情緒</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>同品牌連續 3 次逾時</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>自動開 ChangeRequest</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>報價確認到工單成立</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>問題卡 confirmed</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>建報價 draft
+內部核准
+送客戶
+客戶於 LIFF 查看明細並勾選同意
+確認
+客服 1-click 建立工單</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>工單 created，且無已確認報價不得建單這條硬綁定成立</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>報價確認到工單成立</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>問題卡 confirmed</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>報價過期（一般 14 天／急件 3 天）</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>失效需重報</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>報價確認到工單成立</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>問題卡 confirmed</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>保固／專案案件由 AI 送出</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>403 阻擋</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>報價確認到工單成立</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>問題卡 confirmed</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>客戶端視圖出現成本欄</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>視為重大缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>派工媒合到技師接單</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>工單 created</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>候選池 5
+10
+20km 擴大
+五因子權重排序
+top-1 通知
+技師接單</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>技師接單，工單狀態推進至 assigned，品牌側與技師側投影一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>派工媒合到技師接單</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>工單 created</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>候選池空</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>dispatch_pending + alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>派工媒合到技師接單</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>工單 created</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>接單逾時（一般 10min／急件 5min）</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>回佇列擴大候選</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>派工媒合到技師接單</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>工單 created</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>技師拒單</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>自動改派</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>派工媒合到技師接單</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>工單 created</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>小編手動覆寫</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>必留 who/why 稽核</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>SC-06</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>現場施工到完工結案</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>技師抵達現場並簽到</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>到場存證
+施工
+施工照上傳
+材料登錄（主鎖與高價零件強制 serial）
+客戶簽名
+結案</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>通過結案硬閘（地址齊備 + 報價已確認 + 證據齊備），狀態 completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SC-06</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>現場施工到完工結案</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>技師抵達現場並簽到</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>照片不足／無簽名／缺 serial</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>422 阻擋</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>SC-06</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>現場施工到完工結案</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>技師抵達現場並簽到</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>客戶不在場</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>手機簽章頁 → QR 跨裝置 → 紙本 fallback + audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SC-06</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>現場施工到完工結案</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>技師抵達現場並簽到</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>客戶不在／無法施工</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>改期並依階段計算取消費</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SC-07</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>現場範圍變更與報價修正</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>技師到場後發現實際故障與報修內容不符</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>師傅發起 requote（事由分類 + 項目 diff，不含金額）
+平台驗身分與工單狀態
+品牌定價引擎產生 quote v+1
+依金額三段分層取得同意
+施工</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>新版報價取得對應層級同意後才施工，且全程留痕</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>SC-07</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>現場範圍變更與報價修正</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>技師到場後發現實際故障與報修內容不符</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>非工單 assignee 發起</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>SC-07</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>現場範圍變更與報價修正</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>技師到場後發現實際故障與報修內容不符</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>師傅單獨收款</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>系統攔截</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>SC-07</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>現場範圍變更與報價修正</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>技師到場後發現實際故障與報修內容不符</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>未走分層直接施工</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>視為合約違反</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SC-08</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>收款、取消與退款</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>工單完工待收款，或任一階段發生取消／退款申請</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>三軌支付（現金／Apple Pay／LINE Pay）
+webhook 冪等對帳
+憑證開立；取消依 5+1 階段自動計費；退款依責任分層並執行職責分離雙簽</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>金額與費率表逐檔一致，帳務為 append-only reversal，零錯帳</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>SC-08</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>收款、取消與退款</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>工單完工待收款，或任一階段發生取消／退款申請</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>派工後 0 元取消</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>阻擋</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>SC-08</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>收款、取消與退款</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>工單完工待收款，或任一階段發生取消／退款申請</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>同人同時發起與核准</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>409 SoD 違反</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SC-08</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>收款、取消與退款</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>工單完工待收款，或任一階段發生取消／退款申請</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>現金爭議</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>進 disputes 流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SC-09</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>月結與七帳本對帳</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-02 租戶 Admin（品牌管理者）</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>結算期末</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>七帳本月結批次
+borrow=lend 平衡驗證
+對帳例外以 reason code 分類處理</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>帳本平衡且例外全數有 reason code</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SC-09</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>月結與七帳本對帳</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>L1-CUS</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>PER-OPS-02 租戶 Admin（品牌管理者）</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>結算期末</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>品牌計費與平台彙總不符</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>期末 reconcile 閘門擋住 payout（銜接 SC-13）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>SC-10</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>人工接管與對話不蒸發</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>L1-OPS</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>對話已 escalated，小編決定接手</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>小編於後台接管
+AI 每 turn 前查接管旗標
+接管中 AI 靜音
+小編與客戶訊息持續全量入庫並標記 sender_role</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>接管期間對話零缺漏，且 AI 未再自行回覆</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>SC-10</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>人工接管與對話不蒸發</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>L1-OPS</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>對話已 escalated，小編決定接手</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>接管旗標查詢失敗（5s timeout）</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>fail-soft 不阻斷客人回覆</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>SC-10</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>人工接管與對話不蒸發</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>L1-OPS</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>對話已 escalated，小編決定接手</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>旗標誤判</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>AI 錯誤靜音或錯誤插話，皆為 P0 缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>SC-11</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>例外審批與 SoD 收件匣</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>L1-OPS</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>產生改期 / 例外案件 / 爭議事件</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>例外集中進收件匣
+分派審批者
+依敏感度要求發起／核准／執行三方分離
+裁決留痕</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>所有敏感操作的三方角色互不相同，違反者 100% 被阻擋</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>SC-11</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>例外審批與 SoD 收件匣</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>L1-OPS</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>產生改期 / 例外案件 / 爭議事件</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>任二角色相同</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>SC-11</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>例外審批與 SoD 收件匣</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>L1-OPS</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>PER-OPS-01 品牌營運（派工小編）</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>產生改期 / 例外案件 / 爭議事件</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>審批逾期</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>升級主管</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>SC-12</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>技師註冊、KYC 到品牌授權</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>師傅於獨立技師站台申請註冊</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>OIDC 建立跨租戶技師身分
+填 profile／技能／欲服務品牌
+上傳 KYC 與認證文件（敏感欄加密）
+人工審核
+認證生效
+品牌授權</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>技師身分獨立於任何品牌租戶，且未過准入閘門者不得進入派工候選集</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>SC-12</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>技師註冊、KYC 到品牌授權</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>師傅於獨立技師站台申請註冊</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>文件不齊</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>退件</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>SC-12</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>技師註冊、KYC 到品牌授權</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>師傅於獨立技師站台申請註冊</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>審核未過卻出現在候選集</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>P0 治理缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>SC-13</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>技師跨品牌對帳與佣金請領</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>佣金產生事件累積至結算期</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>各品牌 per-job 計費發事件
+技師平台跨品牌彙總 statement
+技師對帳
+payout</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>statement 與各品牌計費逐筆對得起來，reconcile 閘門通過</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>SC-13</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>技師跨品牌對帳與佣金請領</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>PER-TEC-01 簽約師傅</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>佣金產生事件累積至結算期</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>對帳差異</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>閘門擋住 payout 並開例外案件（銜接 SC-09）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>SC-14</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>認證撤銷與停權即時廣播</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>PER-PLT-01 平台管理員（Super Admin）</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>技師違規、認證到期或主動停權</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>平台發起撤銷
+廣播撤銷事件
+各品牌訂閱後即時移出候選集
+進行中工單改派</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>撤銷後各品牌候選集一致且不再派給該技師；進行中工單有承接方</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>SC-14</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>認證撤銷與停權即時廣播</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>PER-PLT-01 平台管理員（Super Admin）</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>技師違規、認證到期或主動停權</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>事件遺失導致某品牌仍派工</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="42" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>SC-14</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>認證撤銷與停權即時廣播</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>L1-TEC</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>PER-PLT-01 平台管理員（Super Admin）</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>技師違規、認證到期或主動停權</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>進行中工單無人承接</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>升級人工派工</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>知識精煉 HITL 到雙路發布</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>L1-KNW</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>PER-KNW-01 客服主管</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>診斷對話或產品素材進入精煉佇列</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>素材汲取進 bronze
+提煉分流為事實／行為
+Draft Queue
+審核 UI 呈現 diff
+核可／拒絕／退回重煉
+雙路發布（事實進向量語料、行為進 skill 檔）</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>未核可零落地；發布後 agent 行為與檢索結果同步更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="42" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>知識精煉 HITL 到雙路發布</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>L1-KNW</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>PER-KNW-01 客服主管</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>診斷對話或產品素材進入精煉佇列</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>素材來源不屬 bronze 白名單</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>發布前校驗擋下</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>知識精煉 HITL 到雙路發布</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>L1-KNW</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>PER-KNW-01 客服主管</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>診斷對話或產品素材進入精煉佇列</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>繞過審核直接發布</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>必須失敗</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="42" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>SC-16</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>SOP 雙審與 Family Reviewer 覆核</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>L1-KNW</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>PER-KNW-02 Domain Expert（領域專家）</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>高風險 SOP draft 產生</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>客服主管與 Domain Expert 雙簽
+Family Reviewer 覆核（SLA 24h）
+核可後短時間內向量化發布</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>覆核率 100%，且未經覆核的發布嘗試一律失敗</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="42" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>SC-16</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>SOP 雙審與 Family Reviewer 覆核</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>L1-KNW</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>PER-KNW-02 Domain Expert（領域專家）</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>高風險 SOP draft 產生</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>覆核者缺席逾 24h</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>暫停發布並升級</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>SC-16</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>SOP 雙審與 Family Reviewer 覆核</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>L1-KNW</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>PER-KNW-02 Domain Expert（領域專家）</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>高風險 SOP draft 產生</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>ledger 遭竄改</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>稽核鏈驗證失敗</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="42" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>SC-17</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>品牌申請到 License 開通上線</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>PER-PLT-02 潛在加盟品牌</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>潛在品牌於官網送出加盟申請</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>申請受理
+Super Admin 審核
+建立租戶組織與 License
+依 License 決定開通模組
+per-brand 部署、建庫、綁定 LINE 通道
+上線</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>品牌可獨立登入並操作已開通模組，且跨租戶零資料可見性</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>SC-17</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>品牌申請到 License 開通上線</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>PER-PLT-02 潛在加盟品牌</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>潛在品牌於官網送出加盟申請</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>provisioning 中斷</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>可重跑且冪等</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>SC-17</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>品牌申請到 License 開通上線</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>PER-PLT-02 潛在加盟品牌</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>潛在品牌於官網送出加盟申請</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>License 未涵蓋的模組出現在選單</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>治理缺陷</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>品牌自助配置與治理回滾</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>PER-OPS-02 租戶 Admin（品牌管理者）</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>品牌需調整費率、文案、skill 客製層或流程積木</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>於後台編輯
+版本化
+評估閘門
+分階段推出
+觀察
+必要時一鍵回滾</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>配置變更不需改碼即生效，回滾在約定時間內完成，全程留 who/when/what diff/why</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>品牌自助配置與治理回滾</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>PER-OPS-02 租戶 Admin（品牌管理者）</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>品牌需調整費率、文案、skill 客製層或流程積木</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>嘗試覆寫受保護層（escalation／domain-safety）</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>阻擋</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>品牌自助配置與治理回滾</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>PER-OPS-02 租戶 Admin（品牌管理者）</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>品牌需調整費率、文案、skill 客製層或流程積木</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>非 owner 角色嘗試修改</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>阻擋</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>品牌自助配置與治理回滾</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>PER-OPS-02 租戶 Admin（品牌管理者）</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>品牌需調整費率、文案、skill 客製層或流程積木</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>高風險流程由 AI 產出</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>強制人審</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>SC-19</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>GDPR 被遺忘權執行</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>happy 正常路徑</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>資料當事人提出刪除請求</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>受理
+legal-hold 衝突檢查
+T0 銷毀金鑰並軟刪
+T+30 日排程硬刪
+全程寫入 append-only 稽核帳本</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>於法定期限內執行，或在期限內完成客戶告知</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>SC-19</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>GDPR 被遺忘權執行</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>資料當事人提出刪除請求</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>與 legal hold 衝突</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>拒絕並於 7 日內通知客戶</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>SC-19</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>GDPR 被遺忘權執行</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>L1-PLT</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>PER-CUS-01 終端客戶</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>failure 例外</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>資料當事人提出刪除請求</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>硬刪排程未執行</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>合規事故</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H65"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ BDD 行為情境（生成）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 旅程驗收主表'!$A$1:$R$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 旅程驗收主表'!$A$1:$T$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 旅程展開（SC × 需求）'!$A$1:$I$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'④ 旅程 × Persona（誰在走）'!$A$1:$G$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⑤ BDD 行為情境（生成）'!$A$1:$H$65</definedName>
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -798,6 +798,8 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -889,6 +891,16 @@
       <c r="R1" s="3" t="inlineStr">
         <is>
           <t>裁決備註</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Plane 驗收狀態</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Plane 腳本進度</t>
         </is>
       </c>
     </row>
@@ -959,6 +971,16 @@
       <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="6" t="inlineStr"/>
       <c r="R2" s="6" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 13, "passed": 0, "skipped": 0, "total": 13}</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="68" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
@@ -1027,6 +1049,16 @@
       <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 12, "passed": 0, "skipped": 0, "total": 12}</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="68" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -1095,6 +1127,16 @@
       <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="6" t="inlineStr"/>
       <c r="R4" s="6" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="68" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1163,6 +1205,16 @@
       <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="6" t="inlineStr"/>
       <c r="R5" s="6" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 12, "passed": 0, "skipped": 0, "total": 12}</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="68" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1231,6 +1283,16 @@
       <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="6" t="inlineStr"/>
       <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 12, "passed": 0, "skipped": 0, "total": 12}</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="68" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1299,6 +1361,16 @@
       <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="6" t="inlineStr"/>
       <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 15, "passed": 0, "skipped": 0, "total": 15}</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="68" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1367,6 +1439,16 @@
       <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="6" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 7, "passed": 0, "skipped": 0, "total": 7}</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="68" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1435,6 +1517,16 @@
       <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 11, "passed": 0, "skipped": 0, "total": 11}</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="68" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1503,6 +1595,16 @@
       <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="6" t="inlineStr"/>
       <c r="R10" s="6" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 4, "passed": 0, "skipped": 0, "total": 4}</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="68" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1571,6 +1673,16 @@
       <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="6" t="inlineStr"/>
       <c r="R11" s="6" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 5, "passed": 0, "skipped": 0, "total": 5}</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="68" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
@@ -1639,6 +1751,16 @@
       <c r="P12" s="6" t="inlineStr"/>
       <c r="Q12" s="6" t="inlineStr"/>
       <c r="R12" s="6" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 5, "passed": 0, "skipped": 0, "total": 5}</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="68" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -1707,6 +1829,16 @@
       <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="6" t="inlineStr"/>
       <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="68" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -1775,6 +1907,16 @@
       <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="6" t="inlineStr"/>
       <c r="R14" s="6" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 3, "passed": 0, "skipped": 0, "total": 3}</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="68" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -1843,6 +1985,16 @@
       <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="6" t="inlineStr"/>
       <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="68" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
@@ -1911,6 +2063,16 @@
       <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr"/>
       <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="68" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -1979,6 +2141,16 @@
       <c r="P17" s="6" t="inlineStr"/>
       <c r="Q17" s="6" t="inlineStr"/>
       <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 3, "passed": 0, "skipped": 0, "total": 3}</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="68" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -2047,6 +2219,16 @@
       <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="6" t="inlineStr"/>
       <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="68" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -2115,6 +2297,16 @@
       <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="6" t="inlineStr"/>
       <c r="R19" s="6" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="68" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
@@ -2183,9 +2375,19 @@
       <c r="P20" s="6" t="inlineStr"/>
       <c r="Q20" s="6" t="inlineStr"/>
       <c r="R20" s="6" t="inlineStr"/>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>active {"blocked": 0, "failed": 0, "open": 7, "passed": 0, "skipped": 0, "total": 7}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R20"/>
+  <autoFilter ref="A1:T20"/>
   <dataValidations count="1">
     <dataValidation sqref="O2:O20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填四種驗收狀態之一" type="list">
       <formula1>"Not Accepted,Verified,Accepted,Deferred"</formula1>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 旅程驗收主表'!$A$1:$T$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 旅程展開（SC × 需求）'!$A$1:$I$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'④ 旅程 × Persona（誰在走）'!$A$1:$G$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⑤ BDD 行為情境（生成）'!$A$1:$H$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⑤ BDD 行為情境（生成）'!$A$1:$I$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9851,7 +9851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9859,9 +9859,10 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -9892,15 +9893,20 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>涵蓋需求（由 SC 邊推導）</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>Given（前置）</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>When（行為）</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Then（預期）</t>
         </is>
@@ -9932,12 +9938,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-01、FR-AGT-02、FR-AGT-03、FR-AGT-07、FR-AGT-11、NFR-Perf-001、NFR-Comp-003</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>客戶加官方帳號後，詢問一般產品操作或知識問題（如換電池、恢復原廠設定）</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>LINE 進線驗簽
 Turn 編排
@@ -9948,7 +9959,7 @@
 對話結案</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>客戶問題被解答且未產生問題卡；回答內容與知識庫一致，無紅線違反</t>
         </is>
@@ -9980,17 +9991,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-01、FR-AGT-02、FR-AGT-03、FR-AGT-07、FR-AGT-11、NFR-Perf-001、NFR-Comp-003</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>客戶加官方帳號後，詢問一般產品操作或知識問題（如換電池、恢復原廠設定）</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>連續 3 次未釐清</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>自動升級轉真人（落入 SC-02）</t>
         </is>
@@ -10022,17 +10038,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-01、FR-AGT-02、FR-AGT-03、FR-AGT-07、FR-AGT-11、NFR-Perf-001、NFR-Comp-003</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>客戶加官方帳號後，詢問一般產品操作或知識問題（如換電池、恢復原廠設定）</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>詢價誘導</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>只給範圍價、不給確定金額</t>
         </is>
@@ -10064,17 +10085,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-01、FR-AGT-02、FR-AGT-03、FR-AGT-07、FR-AGT-11、NFR-Perf-001、NFR-Comp-003</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>客戶加官方帳號後，詢問一般產品操作或知識問題（如換電池、恢復原廠設定）</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>影像辨識請求</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>一律拒絕（僅存證）</t>
         </is>
@@ -10106,12 +10132,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-03、FR-AGT-05、FR-API-01、FR-API-13、FR-AGT-01、NFR-Perf-001、NFR-Rel-003</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>客戶回報鎖具故障並要求派師傅</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>AI 追問品牌／型號／地址
 三層解決嘗試
@@ -10123,7 +10154,7 @@
 confirmed</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>問題卡狀態為 confirmed，欄位與對話事實一致，badge 標示 AI 草擬來源</t>
         </is>
@@ -10155,17 +10186,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-03、FR-AGT-05、FR-API-01、FR-API-13、FR-AGT-01、NFR-Perf-001、NFR-Rel-003</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>客戶回報鎖具故障並要求派師傅</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>資料連 3 次收不齊</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>自動轉真人</t>
         </is>
@@ -10197,17 +10233,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-03、FR-AGT-05、FR-API-01、FR-API-13、FR-AGT-01、NFR-Perf-001、NFR-Rel-003</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>客戶回報鎖具故障並要求派師傅</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>地址缺失</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>不擋建卡，延後到結案硬擋</t>
         </is>
@@ -10239,17 +10280,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-03、FR-AGT-05、FR-API-01、FR-API-13、FR-AGT-01、NFR-Perf-001、NFR-Rel-003</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>客戶回報鎖具故障並要求派師傅</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>AI 承諾轉接卻未呼叫工具</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>gateway 兜底補一筆 escalation（案子不得蒸發）</t>
         </is>
@@ -10281,12 +10327,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-04、FR-AGT-05、FR-API-04、FR-API-19、NFR-Comp-001、NFR-Rel-003</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>進線內容命中急件四類——受困門外 / 受困室內 / 人身安全風險 / 怒客情緒</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Intent 階段判定急件
 bypass 三層解決
@@ -10295,7 +10346,7 @@
 4 小時內補稽核報價</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>urgency_detected_at 已寫入、TransferEvent 落檔、工單於 SLA 內成立</t>
         </is>
@@ -10327,17 +10378,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-04、FR-AGT-05、FR-API-04、FR-API-19、NFR-Comp-001、NFR-Rel-003</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>進線內容命中急件四類——受困門外 / 受困室內 / 人身安全風險 / 怒客情緒</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>補稽核逾 4 小時</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>alert 升主管</t>
         </is>
@@ -10369,17 +10425,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-04、FR-AGT-05、FR-API-04、FR-API-19、NFR-Comp-001、NFR-Rel-003</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>進線內容命中急件四類——受困門外 / 受困室內 / 人身安全風險 / 怒客情緒</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>同品牌連續 3 次逾時</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>自動開 ChangeRequest</t>
         </is>
@@ -10411,12 +10472,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-02、FR-API-03、FR-API-04、FR-WEB-06</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>問題卡 confirmed</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>建報價 draft
 內部核准
@@ -10426,7 +10492,7 @@
 客服 1-click 建立工單</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>工單 created，且無已確認報價不得建單這條硬綁定成立</t>
         </is>
@@ -10458,17 +10524,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-02、FR-API-03、FR-API-04、FR-WEB-06</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>問題卡 confirmed</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>報價過期（一般 14 天／急件 3 天）</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>失效需重報</t>
         </is>
@@ -10500,17 +10571,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-02、FR-API-03、FR-API-04、FR-WEB-06</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>問題卡 confirmed</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>保固／專案案件由 AI 送出</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>403 阻擋</t>
         </is>
@@ -10542,17 +10618,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-02、FR-API-03、FR-API-04、FR-WEB-06</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>問題卡 confirmed</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>客戶端視圖出現成本欄</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>視為重大缺陷</t>
         </is>
@@ -10584,12 +10665,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-05、FR-API-07、FR-TEC-03、FR-TEC-04、NFR-Perf-007、NFR-Perf-008、NFR-SLA-002</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>工單 created</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>候選池 5
 10
@@ -10599,7 +10685,7 @@
 技師接單</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>技師接單，工單狀態推進至 assigned，品牌側與技師側投影一致</t>
         </is>
@@ -10631,17 +10717,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-05、FR-API-07、FR-TEC-03、FR-TEC-04、NFR-Perf-007、NFR-Perf-008、NFR-SLA-002</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>工單 created</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>候選池空</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>dispatch_pending + alert</t>
         </is>
@@ -10673,17 +10764,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-05、FR-API-07、FR-TEC-03、FR-TEC-04、NFR-Perf-007、NFR-Perf-008、NFR-SLA-002</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>工單 created</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>接單逾時（一般 10min／急件 5min）</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>回佇列擴大候選</t>
         </is>
@@ -10715,17 +10811,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-05、FR-API-07、FR-TEC-03、FR-TEC-04、NFR-Perf-007、NFR-Perf-008、NFR-SLA-002</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>工單 created</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>技師拒單</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>自動改派</t>
         </is>
@@ -10757,17 +10858,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-05、FR-API-07、FR-TEC-03、FR-TEC-04、NFR-Perf-007、NFR-Perf-008、NFR-SLA-002</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>工單 created</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>小編手動覆寫</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>必留 who/why 稽核</t>
         </is>
@@ -10799,12 +10905,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-08、FR-API-09、FR-TEC-04、FR-TEC-05、NFR-SLA-001、NFR-Comp-003</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>技師抵達現場並簽到</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>到場存證
 施工
@@ -10814,7 +10925,7 @@
 結案</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>通過結案硬閘（地址齊備 + 報價已確認 + 證據齊備），狀態 completed</t>
         </is>
@@ -10846,17 +10957,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-08、FR-API-09、FR-TEC-04、FR-TEC-05、NFR-SLA-001、NFR-Comp-003</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>技師抵達現場並簽到</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>照片不足／無簽名／缺 serial</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>422 阻擋</t>
         </is>
@@ -10888,17 +11004,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-08、FR-API-09、FR-TEC-04、FR-TEC-05、NFR-SLA-001、NFR-Comp-003</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>技師抵達現場並簽到</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>客戶不在場</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>手機簽章頁 → QR 跨裝置 → 紙本 fallback + audit</t>
         </is>
@@ -10930,17 +11051,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-08、FR-API-09、FR-TEC-04、FR-TEC-05、NFR-SLA-001、NFR-Comp-003</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>技師抵達現場並簽到</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>客戶不在／無法施工</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>改期並依階段計算取消費</t>
         </is>
@@ -10972,12 +11098,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-07、FR-API-02、FR-API-03、FR-API-08</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>技師到場後發現實際故障與報修內容不符</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>師傅發起 requote（事由分類 + 項目 diff，不含金額）
 平台驗身分與工單狀態
@@ -10986,7 +11117,7 @@
 施工</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>新版報價取得對應層級同意後才施工，且全程留痕</t>
         </is>
@@ -11018,17 +11149,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-07、FR-API-02、FR-API-03、FR-API-08</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>技師到場後發現實際故障與報修內容不符</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>非工單 assignee 發起</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>403</t>
         </is>
@@ -11060,17 +11196,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-07、FR-API-02、FR-API-03、FR-API-08</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>技師到場後發現實際故障與報修內容不符</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>師傅單獨收款</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>系統攔截</t>
         </is>
@@ -11102,17 +11243,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-07、FR-API-02、FR-API-03、FR-API-08</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>技師到場後發現實際故障與報修內容不符</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>未走分層直接施工</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>視為合約違反</t>
         </is>
@@ -11144,19 +11290,24 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-10、FR-API-11、FR-API-18</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>工單完工待收款，或任一階段發生取消／退款申請</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>三軌支付（現金／Apple Pay／LINE Pay）
 webhook 冪等對帳
 憑證開立；取消依 5+1 階段自動計費；退款依責任分層並執行職責分離雙簽</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>金額與費率表逐檔一致，帳務為 append-only reversal，零錯帳</t>
         </is>
@@ -11188,17 +11339,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-10、FR-API-11、FR-API-18</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>工單完工待收款，或任一階段發生取消／退款申請</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>派工後 0 元取消</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>阻擋</t>
         </is>
@@ -11230,17 +11386,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-10、FR-API-11、FR-API-18</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>工單完工待收款，或任一階段發生取消／退款申請</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>同人同時發起與核准</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>409 SoD 違反</t>
         </is>
@@ -11272,17 +11433,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-10、FR-API-11、FR-API-18</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>工單完工待收款，或任一階段發生取消／退款申請</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>現金爭議</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>進 disputes 流程</t>
         </is>
@@ -11314,19 +11480,24 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-12、FR-API-11、FR-TEC-06</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>結算期末</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>七帳本月結批次
 borrow=lend 平衡驗證
 對帳例外以 reason code 分類處理</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>帳本平衡且例外全數有 reason code</t>
         </is>
@@ -11358,17 +11529,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-12、FR-API-11、FR-TEC-06</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>結算期末</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>品牌計費與平台彙總不符</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>期末 reconcile 閘門擋住 payout（銜接 SC-13）</t>
         </is>
@@ -11400,12 +11576,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-09、FR-API-13、FR-AGT-05、FR-WEB-03</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>對話已 escalated，小編決定接手</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>小編於後台接管
 AI 每 turn 前查接管旗標
@@ -11413,7 +11594,7 @@
 小編與客戶訊息持續全量入庫並標記 sender_role</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>接管期間對話零缺漏，且 AI 未再自行回覆</t>
         </is>
@@ -11445,17 +11626,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-09、FR-API-13、FR-AGT-05、FR-WEB-03</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>對話已 escalated，小編決定接手</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>接管旗標查詢失敗（5s timeout）</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>fail-soft 不阻斷客人回覆</t>
         </is>
@@ -11487,17 +11673,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>FR-AGT-09、FR-API-13、FR-AGT-05、FR-WEB-03</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
         <is>
           <t>對話已 escalated，小編決定接手</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>旗標誤判</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>AI 錯誤靜音或錯誤插話，皆為 P0 缺陷</t>
         </is>
@@ -11529,12 +11720,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-18、FR-PLT-02</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>產生改期 / 例外案件 / 爭議事件</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>例外集中進收件匣
 分派審批者
@@ -11542,7 +11738,7 @@
 裁決留痕</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>所有敏感操作的三方角色互不相同，違反者 100% 被阻擋</t>
         </is>
@@ -11574,17 +11770,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-18、FR-PLT-02</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>產生改期 / 例外案件 / 爭議事件</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>任二角色相同</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>403</t>
         </is>
@@ -11616,17 +11817,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-18、FR-PLT-02</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>產生改期 / 例外案件 / 爭議事件</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>審批逾期</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>升級主管</t>
         </is>
@@ -11658,12 +11864,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-01、FR-TEC-02、FR-PLT-01、FR-PLT-09</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>師傅於獨立技師站台申請註冊</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>OIDC 建立跨租戶技師身分
 填 profile／技能／欲服務品牌
@@ -11673,7 +11884,7 @@
 品牌授權</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>技師身分獨立於任何品牌租戶，且未過准入閘門者不得進入派工候選集</t>
         </is>
@@ -11705,17 +11916,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-01、FR-TEC-02、FR-PLT-01、FR-PLT-09</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>師傅於獨立技師站台申請註冊</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>文件不齊</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>退件</t>
         </is>
@@ -11747,17 +11963,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-01、FR-TEC-02、FR-PLT-01、FR-PLT-09</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>師傅於獨立技師站台申請註冊</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>審核未過卻出現在候選集</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>P0 治理缺陷</t>
         </is>
@@ -11789,12 +12010,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-06、FR-API-12</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>佣金產生事件累積至結算期</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>各品牌 per-job 計費發事件
 技師平台跨品牌彙總 statement
@@ -11802,7 +12028,7 @@
 payout</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>statement 與各品牌計費逐筆對得起來，reconcile 閘門通過</t>
         </is>
@@ -11834,17 +12060,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-06、FR-API-12</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>佣金產生事件累積至結算期</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="H46" s="8" t="inlineStr">
         <is>
           <t>對帳差異</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>閘門擋住 payout 並開例外案件（銜接 SC-09）</t>
         </is>
@@ -11876,12 +12107,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-08、FR-TEC-02、FR-TEC-03、FR-API-05</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>技師違規、認證到期或主動停權</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>平台發起撤銷
 廣播撤銷事件
@@ -11889,7 +12125,7 @@
 進行中工單改派</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>撤銷後各品牌候選集一致且不再派給該技師；進行中工單有承接方</t>
         </is>
@@ -11921,17 +12157,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-08、FR-TEC-02、FR-TEC-03、FR-API-05</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>技師違規、認證到期或主動停權</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>事件遺失導致某品牌仍派工</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -11963,17 +12204,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>FR-TEC-08、FR-TEC-02、FR-TEC-03、FR-API-05</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>技師違規、認證到期或主動停權</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>進行中工單無人承接</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>升級人工派工</t>
         </is>
@@ -12005,12 +12251,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>FR-REF-01、FR-REF-02、FR-REF-03、FR-REF-04、FR-DAT-01、NFR-PUB-001、NFR-PUB-002、NFR-PUB-003、NFR-PUB-004</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
         <is>
           <t>診斷對話或產品素材進入精煉佇列</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr">
         <is>
           <t>素材汲取進 bronze
 提煉分流為事實／行為
@@ -12020,7 +12271,7 @@
 雙路發布（事實進向量語料、行為進 skill 檔）</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>未核可零落地；發布後 agent 行為與檢索結果同步更新</t>
         </is>
@@ -12052,17 +12303,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>FR-REF-01、FR-REF-02、FR-REF-03、FR-REF-04、FR-DAT-01、NFR-PUB-001、NFR-PUB-002、NFR-PUB-003、NFR-PUB-004</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>診斷對話或產品素材進入精煉佇列</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t>素材來源不屬 bronze 白名單</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="I51" s="9" t="inlineStr">
         <is>
           <t>發布前校驗擋下</t>
         </is>
@@ -12094,17 +12350,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>FR-REF-01、FR-REF-02、FR-REF-03、FR-REF-04、FR-DAT-01、NFR-PUB-001、NFR-PUB-002、NFR-PUB-003、NFR-PUB-004</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
         <is>
           <t>診斷對話或產品素材進入精煉佇列</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
+      <c r="H52" s="9" t="inlineStr">
         <is>
           <t>繞過審核直接發布</t>
         </is>
       </c>
-      <c r="H52" s="9" t="inlineStr">
+      <c r="I52" s="9" t="inlineStr">
         <is>
           <t>必須失敗</t>
         </is>
@@ -12136,19 +12397,24 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>FR-REF-05、FR-REF-03、FR-REF-04、NFR-Comp-002</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>高風險 SOP draft 產生</t>
         </is>
       </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="H53" s="9" t="inlineStr">
         <is>
           <t>客服主管與 Domain Expert 雙簽
 Family Reviewer 覆核（SLA 24h）
 核可後短時間內向量化發布</t>
         </is>
       </c>
-      <c r="H53" s="9" t="inlineStr">
+      <c r="I53" s="9" t="inlineStr">
         <is>
           <t>覆核率 100%，且未經覆核的發布嘗試一律失敗</t>
         </is>
@@ -12180,17 +12446,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>FR-REF-05、FR-REF-03、FR-REF-04、NFR-Comp-002</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>高風險 SOP draft 產生</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>覆核者缺席逾 24h</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>暫停發布並升級</t>
         </is>
@@ -12222,17 +12493,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>FR-REF-05、FR-REF-03、FR-REF-04、NFR-Comp-002</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
         <is>
           <t>高風險 SOP draft 產生</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
+      <c r="H55" s="9" t="inlineStr">
         <is>
           <t>ledger 遭竄改</t>
         </is>
       </c>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="I55" s="9" t="inlineStr">
         <is>
           <t>稽核鏈驗證失敗</t>
         </is>
@@ -12264,12 +12540,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-03、FR-PLT-01、FR-PLT-09、FR-DAT-03</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>潛在品牌於官網送出加盟申請</t>
         </is>
       </c>
-      <c r="G56" s="10" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>申請受理
 Super Admin 審核
@@ -12279,7 +12560,7 @@
 上線</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>品牌可獨立登入並操作已開通模組，且跨租戶零資料可見性</t>
         </is>
@@ -12311,17 +12592,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-03、FR-PLT-01、FR-PLT-09、FR-DAT-03</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>潛在品牌於官網送出加盟申請</t>
         </is>
       </c>
-      <c r="G57" s="10" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>provisioning 中斷</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>可重跑且冪等</t>
         </is>
@@ -12353,17 +12639,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F58" s="10" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-03、FR-PLT-01、FR-PLT-09、FR-DAT-03</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>潛在品牌於官網送出加盟申請</t>
         </is>
       </c>
-      <c r="G58" s="10" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>License 未涵蓋的模組出現在選單</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>治理缺陷</t>
         </is>
@@ -12395,12 +12686,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-08、FR-PLT-07、FR-PLT-02、NFR-Perf-010</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
         <is>
           <t>品牌需調整費率、文案、skill 客製層或流程積木</t>
         </is>
       </c>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>於後台編輯
 版本化
@@ -12410,7 +12706,7 @@
 必要時一鍵回滾</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>配置變更不需改碼即生效，回滾在約定時間內完成，全程留 who/when/what diff/why</t>
         </is>
@@ -12442,17 +12738,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-08、FR-PLT-07、FR-PLT-02、NFR-Perf-010</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
         <is>
           <t>品牌需調整費率、文案、skill 客製層或流程積木</t>
         </is>
       </c>
-      <c r="G60" s="10" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>嘗試覆寫受保護層（escalation／domain-safety）</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>阻擋</t>
         </is>
@@ -12484,17 +12785,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-08、FR-PLT-07、FR-PLT-02、NFR-Perf-010</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
         <is>
           <t>品牌需調整費率、文案、skill 客製層或流程積木</t>
         </is>
       </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>非 owner 角色嘗試修改</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>阻擋</t>
         </is>
@@ -12526,17 +12832,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>FR-PLT-08、FR-PLT-07、FR-PLT-02、NFR-Perf-010</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
         <is>
           <t>品牌需調整費率、文案、skill 客製層或流程積木</t>
         </is>
       </c>
-      <c r="G62" s="10" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>高風險流程由 AI 產出</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>強制人審</t>
         </is>
@@ -12568,12 +12879,17 @@
           <t>happy 正常路徑</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-16、FR-API-15、FR-DAT-06、NFR-Comp-004</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>資料當事人提出刪除請求</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>受理
 legal-hold 衝突檢查
@@ -12582,7 +12898,7 @@
 全程寫入 append-only 稽核帳本</t>
         </is>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>於法定期限內執行，或在期限內完成客戶告知</t>
         </is>
@@ -12614,17 +12930,22 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-16、FR-API-15、FR-DAT-06、NFR-Comp-004</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
         <is>
           <t>資料當事人提出刪除請求</t>
         </is>
       </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>與 legal hold 衝突</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>拒絕並於 7 日內通知客戶</t>
         </is>
@@ -12656,24 +12977,29 @@
           <t>failure 例外</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>FR-API-16、FR-API-15、FR-DAT-06、NFR-Comp-004</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>資料當事人提出刪除請求</t>
         </is>
       </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>硬刪排程未執行</t>
         </is>
       </c>
-      <c r="H65" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>合規事故</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H65"/>
+  <autoFilter ref="A1:I65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>工程證據＝關鍵路徑上 FR 的 code reality 分佈；測試覆蓋＝關鍵需求裡有幾條有案例；驗收腳本＝這條旅程在 UAT 有沒有腳本。三個都綠才代表「可以開始驗收」，不代表「已驗收」。</t>
+          <t>工程證據＝關鍵路徑上 FR 的 code reality 分佈；驗收契約覆蓋＝關鍵需求裡有幾條有契約；驗收腳本＝這條旅程在 UAT 有沒有腳本。三個都綠才代表「可以開始驗收」，不代表「已驗收」。</t>
         </is>
       </c>
     </row>
@@ -630,137 +630,249 @@
       <c r="A8" s="1" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>黃色欄位</t>
+          <t>Plane 詞彙對照</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>只有人能填。系統不會、也不該幫你填。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
+          <t>本書的列在 Plane 專案管理系統裡叫什麼（依《Plane QA 工程守則》Part B）。跨系統討論一律用右欄的名字——同一件事兩個名字，是對帳失敗最常見的起點。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>灰色欄位</t>
+          <t xml:space="preserve">  旅程 SC</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
+          <t>Plane 的 Scenario 型別卡。「刻意不進 Epic/Feature/Story 階層樹」——一張卡只能有一個 parent，而旅程橫跨多個子系統，硬掛進樹會逼它選一個歸屬。它改為直接持有自己的驗收契約。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>白色欄位</t>
+          <t xml:space="preserve">  分線 L1-CUS…</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>正典敘述，同樣改上游。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="1" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr"/>
+          <t>Plane 的 Module（範疇分組）。⚠️ 敏捷文獻常把這種價值主軸叫 Epic，但本專案的 Epic 另有所指（＝子系統，見上），兩者不可混用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  關鍵需求 / 支援需求</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Plane 需求卡上的 essential_for / supporting_for 兩個欄位。邊的屬性在 Plane 掛不上關聯（relation 不能帶屬性），所以降維成節點屬性。</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>四個狀態軸不得互推</t>
+          <t xml:space="preserve">  驗收契約</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
+          <t>Plane 的 Test Case。守則把 FR／驗收條件／BDD／測試案例壓成「同一個物件」——案例就是驗收條件，省掉一整層追蹤。所以本書講「案例」與講「契約」是同一件事。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>怎麼重生</t>
+          <t xml:space="preserve">  驗收腳本 ＝ 一條旅程一條</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>改上游正典 → 在 規格統控整理/ 跑 python3 _build_workbooks.py。xlsx 是單向快照，永遠不要直接改 xlsx 再往回抄。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="1" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
+          <t>本欄就是這條 SC 在 Plane 的 Test Run（19 條 SC＝19 條 run），內容是該 SC 宣告的那批案例。建立 run 時把每張案例釘在當時的版本，所以舊紀錄不會被日後改版影響。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  括號裡的 UAT-01…UAT-09</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>22_UAT_Report §4 的走查腳本編號，是「旅程的上層分組」：一支走查涵蓋 1–4 條旅程（UAT-01 撐 SC-01/02/03、UAT-02 撐 SC-04–07）。它回答「這次 UAT 要走哪條路線」，而旅程回答「路線裡的這一段」。⚠️ 它在 Plane 沒有對應物件，只被寫進 run 名稱當註記。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>RACI</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+          <t xml:space="preserve">  標「不走 UAT 走查」的旅程</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>那條旅程宣告 uat: null——它一樣有自己的 run 與案例，只是不掛在任何一支走查腳本下。月結 cron、七帳本對帳這類後端受控驗收沒有人能「走一遍」給你看，硬編一支走查腳本只是造假。它不是缺口，V9 也不會報它；空著不寫才會跟「漏填」混在一起。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  旅程敘述</t>
+          <t xml:space="preserve">  驗收狀態</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>R: BA　A: PM　來源: 28_Scenarios.md</t>
+          <t>Plane 的 SC 卡 state。這是四個狀態軸裡的軸④，「只有人能推進」——測試全綠、閘門 ready 都不等於驗收通過。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  旅程需要哪些需求</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>R: SA　A: 架構師　來源: _relations/sc_requires_rq.yaml</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  工程證據</t>
+          <t>黃色欄位</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>R: RD　A: 架構師　來源: _spec_data.py codebase 掃描</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+          <t>只有人能填。系統不會、也不該幫你填。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  測試覆蓋 / 驗收腳本</t>
+          <t>灰色欄位</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>R: QA　A: QA Lead　來源: _relations/rq_verified_by_tc.yaml、sc_verified_by_tc.yaml</t>
+          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>白色欄位</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>正典敘述，同樣改上游。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="1" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>四個狀態軸不得互推</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>怎麼重生</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>改上游正典 → 在 規格統控整理/ 跑 python3 _build_workbooks.py。xlsx 是單向快照，永遠不要直接改 xlsx 再往回抄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="1" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>RACI</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  旅程敘述</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>R: BA　A: PM　來源: 28_Scenarios.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  旅程需要哪些需求</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>R: SA　A: 架構師　來源: _relations/sc_requires_rq.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  工程證據</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>R: RD　A: 架構師　來源: _spec_data.py codebase 掃描</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  驗收契約覆蓋 / 驗收腳本</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>R: QA　A: QA Lead　來源: _relations/rq_verified_by_tc.yaml、sc_verified_by_tc.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">  驗收狀態（黃）</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>R: 業務 Owner　A: PM　只有人能推進</t>
         </is>
@@ -791,8 +903,8 @@
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
@@ -860,12 +972,12 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t>測試覆蓋</t>
+          <t>驗收契約覆蓋</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
         <is>
-          <t>驗收腳本</t>
+          <t>驗收腳本（TestRun）</t>
         </is>
       </c>
       <c r="N1" s="3" t="inlineStr">
@@ -963,7 +1075,7 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>S1：13 案例</t>
+          <t>13 案例（UAT-01）</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr"/>
@@ -1041,7 +1153,7 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>S1：12 案例</t>
+          <t>12 案例（UAT-01）</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr"/>
@@ -1119,7 +1231,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>S1：6 案例</t>
+          <t>6 案例（UAT-01）</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr"/>
@@ -1197,7 +1309,7 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>S2：12 案例</t>
+          <t>12 案例（UAT-02）</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr"/>
@@ -1275,7 +1387,7 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>S2：12 案例</t>
+          <t>12 案例（UAT-02）</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr"/>
@@ -1353,7 +1465,7 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>S2：15 案例</t>
+          <t>15 案例（UAT-02）</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr"/>
@@ -1431,7 +1543,7 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>S2：7 案例</t>
+          <t>7 案例（UAT-02）</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr"/>
@@ -1509,7 +1621,7 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>S4：11 案例</t>
+          <t>11 案例（UAT-04）</t>
         </is>
       </c>
       <c r="N9" s="5" t="inlineStr"/>
@@ -1587,7 +1699,7 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>4 案例</t>
+          <t>4 案例（不走 UAT 走查）</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr"/>
@@ -1665,7 +1777,7 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>S6：5 案例</t>
+          <t>5 案例（UAT-06）</t>
         </is>
       </c>
       <c r="N11" s="5" t="inlineStr"/>
@@ -1743,7 +1855,7 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>S4：5 案例</t>
+          <t>5 案例（UAT-04）</t>
         </is>
       </c>
       <c r="N12" s="5" t="inlineStr"/>
@@ -1821,7 +1933,7 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>S7：6 案例</t>
+          <t>6 案例（UAT-07）</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr"/>
@@ -1899,7 +2011,7 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>3 案例</t>
+          <t>3 案例（不走 UAT 走查）</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr"/>
@@ -1977,7 +2089,7 @@
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>S8：6 案例</t>
+          <t>6 案例（UAT-08）</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr"/>
@@ -2055,7 +2167,7 @@
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>S3：6 案例</t>
+          <t>6 案例（UAT-03）</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr"/>
@@ -2133,7 +2245,7 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>S3：3 案例</t>
+          <t>3 案例（UAT-03）</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr"/>
@@ -2211,7 +2323,7 @@
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>S9：6 案例</t>
+          <t>6 案例（UAT-09）</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr"/>
@@ -2289,7 +2401,7 @@
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>S5：6 案例</t>
+          <t>6 案例（UAT-05）</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr"/>
@@ -2367,7 +2479,7 @@
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>S4：7 案例</t>
+          <t>7 案例（UAT-04）</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr"/>
@@ -2455,7 +2567,7 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>測試覆蓋</t>
+          <t>涵蓋 kind</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ BDD 行為情境（生成）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 旅程驗收主表'!$A$1:$T$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 旅程驗收主表'!$A$1:$U$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'③ 旅程展開（SC × 需求）'!$A$1:$I$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'④ 旅程 × Persona（誰在走）'!$A$1:$G$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'⑤ BDD 行為情境（生成）'!$A$1:$I$65</definedName>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>不在這本裡的東西</t>
@@ -622,257 +622,269 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>可用性、稽核鏈、安全矩陣、migration 可重現、效能降級——這些沒有對應的客戶旅程，為它們硬掰一段客戶語言就是造假。它們宣告為 scope: global，在《整合測試計畫》③ 獨立成段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Plane 詞彙對照</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>本書的列在 Plane 專案管理系統裡叫什麼（依《Plane QA 工程守則》Part B）。跨系統討論一律用右欄的名字——同一件事兩個名字，是對帳失敗最常見的起點。</t>
-        </is>
-      </c>
+          <t>可用性、稽核鏈、安全矩陣、migration 可重現、效能降級——這些沒有對應的客戶旅程，為它們硬掰一段客戶語言就是造假。它們宣告為 scope: global，掛在《模組功能 BOM》的跨旅程地板 E-GLB 底下，並在《整合測試計畫》③ 獨立成段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>② 的「Plane Feature」欄是什麼（2026-08-05 新增）</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>旅程在 Plane 從「樹外的獨立卡」改成拆解樹上的 Feature，掛在自己那條價值線 Epic 底下。這欄標明它的位置。意義在覆蓋率：數字現在沿 需求 → 旅程 → 價值線 往上加總，「哪幾條客戶旅程跑得通」才第一次有載體答得出來。旅程既有的驗收契約不受影響。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="1" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>Plane 詞彙對照</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>本書的列在 Plane 專案管理系統裡叫什麼（依《Plane QA 工程守則》Part B）。跨系統討論一律用右欄的名字——同一件事兩個名字，是對帳失敗最常見的起點。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">  旅程 SC</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Plane 的 Scenario 型別卡。「刻意不進 Epic/Feature/Story 階層樹」——一張卡只能有一個 parent，而旅程橫跨多個子系統，硬掛進樹會逼它選一個歸屬。它改為直接持有自己的驗收契約。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  分線 L1-CUS…</t>
-        </is>
-      </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Plane 的 Module（範疇分組）。⚠️ 敏捷文獻常把這種價值主軸叫 Epic，但本專案的 Epic 另有所指（＝子系統，見上），兩者不可混用。</t>
+          <t>Plane 的 Feature（level 1），**在拆解樹上**（2026-08-05 形狀變更）。舊版讓它留在樹外，理由是「一張卡只有一個 parent，而旅程橫跨多個子系統」；Epic 換成價值線之後這個理由消失了——旅程本來就只屬於一條價值線。覆蓋率因此沿 Story → SC → 價值線 roll-up，管理層才答得出「哪幾條旅程跑得通」。它既有的「直接持有驗收契約」不變，與 parent 鏈並存。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  關鍵需求 / 支援需求</t>
+          <t xml:space="preserve">  分線 L1-CUS…</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Plane 需求卡上的 essential_for / supporting_for 兩個欄位。邊的屬性在 Plane 掛不上關聯（relation 不能帶屬性），所以降維成節點屬性。</t>
+          <t>Plane 的 Epic（E-CUS…E-PLT，level 0，is_epic=true）。⚠️ 2026-08-05 前寫的是「Plane 的 Module」，已作廢——Module 現在是 7 個子系統。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  驗收契約</t>
+          <t xml:space="preserve">  關鍵需求 / 支援需求</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Plane 的 Test Case。守則把 FR／驗收條件／BDD／測試案例壓成「同一個物件」——案例就是驗收條件，省掉一整層追蹤。所以本書講「案例」與講「契約」是同一件事。</t>
+          <t>Plane 需求卡上的 essential_for / supporting_for 兩個欄位。邊的屬性在 Plane 掛不上關聯（relation 不能帶屬性），所以降維成節點屬性。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">  驗收契約</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Plane 的 Test Case。守則把 FR／驗收條件／BDD／測試案例壓成「同一個物件」——案例就是驗收條件，省掉一整層追蹤。所以本書講「案例」與講「契約」是同一件事。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">  驗收腳本 ＝ 一條旅程一條</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>本欄就是這條 SC 在 Plane 的 Test Run（19 條 SC＝19 條 run），內容是該 SC 宣告的那批案例。建立 run 時把每張案例釘在當時的版本，所以舊紀錄不會被日後改版影響。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  括號裡的 UAT-01…UAT-09</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>22_UAT_Report §4 的走查腳本編號，是「旅程的上層分組」：一支走查涵蓋 1–4 條旅程（UAT-01 撐 SC-01/02/03、UAT-02 撐 SC-04–07）。它回答「這次 UAT 要走哪條路線」，而旅程回答「路線裡的這一段」。⚠️ 它在 Plane 沒有對應物件，只被寫進 run 名稱當註記。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">  括號裡的 UAT-01…UAT-09</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>22_UAT_Report §4 的走查腳本編號，是「旅程的上層分組」：一支走查涵蓋 1–4 條旅程（UAT-01 撐 SC-01/02/03、UAT-02 撐 SC-04–07）。它回答「這次 UAT 要走哪條路線」，而旅程回答「路線裡的這一段」。⚠️ 它在 Plane 沒有對應物件，只被寫進 run 名稱當註記。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">  標「不走 UAT 走查」的旅程</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>那條旅程宣告 uat: null——它一樣有自己的 run 與案例，只是不掛在任何一支走查腳本下。月結 cron、七帳本對帳這類後端受控驗收沒有人能「走一遍」給你看，硬編一支走查腳本只是造假。它不是缺口，V9 也不會報它；空著不寫才會跟「漏填」混在一起。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  驗收狀態</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Plane 的 SC 卡 state。這是四個狀態軸裡的軸④，「只有人能推進」——測試全綠、閘門 ready 都不等於驗收通過。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="1" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr"/>
-    </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>黃色欄位</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>只有人能填。系統不會、也不該幫你填。</t>
-        </is>
-      </c>
+      <c r="A19" s="1" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>灰色欄位</t>
+          <t>黃色欄位</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
+          <t>只有人能填。系統不會、也不該幫你填。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>灰色欄位</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>生成欄，手改會在下次重跑被覆蓋。要改請改上游 Markdown 或 _relations/*.yaml。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>白色欄位</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>正典敘述，同樣改上游。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="1" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>四個狀態軸不得互推</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
-        </is>
-      </c>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
+          <t>四個狀態軸不得互推</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>程式檔存在 ≠ 工程完成；工程完成 ≠ 測試通過；測試通過 ≠ 驗收通過。需求定版(SA) / 工程證據(RD) / 測試執行(QA) / 驗收通過(業務 Owner) 各有唯一 owner，任何一格都不得由另一軸自動帶出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
           <t>怎麼重生</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>改上游正典 → 在 規格統控整理/ 跑 python3 _build_workbooks.py。xlsx 是單向快照，永遠不要直接改 xlsx 再往回抄。</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr"/>
-    </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>RACI</t>
-        </is>
-      </c>
+      <c r="A26" s="1" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  旅程敘述</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>R: BA　A: PM　來源: 28_Scenarios.md</t>
-        </is>
-      </c>
+          <t>RACI</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  旅程需要哪些需求</t>
+          <t xml:space="preserve">  旅程敘述</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>R: SA　A: 架構師　來源: _relations/sc_requires_rq.yaml</t>
+          <t>R: BA　A: PM　來源: 28_Scenarios.md</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">  旅程需要哪些需求</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>R: SA　A: 架構師　來源: _relations/sc_requires_rq.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">  工程證據</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>R: RD　A: 架構師　來源: _spec_data.py codebase 掃描</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  驗收契約覆蓋 / 驗收腳本</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>R: QA　A: QA Lead　來源: _relations/rq_verified_by_tc.yaml、sc_verified_by_tc.yaml</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">  驗收狀態（黃）</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>R: 業務 Owner　A: PM　只有人能推進</t>
         </is>
@@ -889,7 +901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -910,8 +922,9 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1007,10 +1020,15 @@
       </c>
       <c r="S1" s="3" t="inlineStr">
         <is>
+          <t>Plane Feature</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
           <t>Plane 驗收狀態</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Plane 腳本進度</t>
         </is>
@@ -1085,10 +1103,15 @@
       <c r="R2" s="6" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-01 ⊂ E-CUS 終端客戶價值線</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="U2" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 13, "passed": 0, "skipped": 0, "total": 13}</t>
         </is>
@@ -1163,10 +1186,15 @@
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-02 ⊂ E-CUS 終端客戶價值線</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 12, "passed": 0, "skipped": 0, "total": 12}</t>
         </is>
@@ -1241,10 +1269,15 @@
       <c r="R4" s="6" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-03 ⊂ E-CUS 終端客戶價值線</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
         </is>
@@ -1319,10 +1352,15 @@
       <c r="R5" s="6" t="inlineStr"/>
       <c r="S5" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-04 ⊂ E-CUS 終端客戶價值線</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr">
+      <c r="U5" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 12, "passed": 0, "skipped": 0, "total": 12}</t>
         </is>
@@ -1397,10 +1435,15 @@
       <c r="R6" s="6" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-05 ⊂ E-CUS 終端客戶價值線</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr">
+      <c r="U6" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 12, "passed": 0, "skipped": 0, "total": 12}</t>
         </is>
@@ -1475,10 +1518,15 @@
       <c r="R7" s="6" t="inlineStr"/>
       <c r="S7" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-06 ⊂ E-CUS 終端客戶價值線</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 15, "passed": 0, "skipped": 0, "total": 15}</t>
         </is>
@@ -1553,10 +1601,15 @@
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-07 ⊂ E-CUS 終端客戶價值線</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T8" s="5" t="inlineStr">
+      <c r="U8" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 7, "passed": 0, "skipped": 0, "total": 7}</t>
         </is>
@@ -1631,10 +1684,15 @@
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-08 ⊂ E-CUS 終端客戶價值線</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T9" s="5" t="inlineStr">
+      <c r="U9" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 11, "passed": 0, "skipped": 0, "total": 11}</t>
         </is>
@@ -1709,10 +1767,15 @@
       <c r="R10" s="6" t="inlineStr"/>
       <c r="S10" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-09 ⊂ E-CUS 終端客戶價值線</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr">
+      <c r="U10" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 4, "passed": 0, "skipped": 0, "total": 4}</t>
         </is>
@@ -1787,10 +1850,15 @@
       <c r="R11" s="6" t="inlineStr"/>
       <c r="S11" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-10 ⊂ E-OPS 品牌營運價值線</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T11" s="5" t="inlineStr">
+      <c r="U11" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 5, "passed": 0, "skipped": 0, "total": 5}</t>
         </is>
@@ -1865,10 +1933,15 @@
       <c r="R12" s="6" t="inlineStr"/>
       <c r="S12" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-11 ⊂ E-OPS 品牌營運價值線</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T12" s="5" t="inlineStr">
+      <c r="U12" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 5, "passed": 0, "skipped": 0, "total": 5}</t>
         </is>
@@ -1943,10 +2016,15 @@
       <c r="R13" s="6" t="inlineStr"/>
       <c r="S13" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-12 ⊂ E-TEC 簽約師傅價值線</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T13" s="5" t="inlineStr">
+      <c r="U13" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
         </is>
@@ -2021,10 +2099,15 @@
       <c r="R14" s="6" t="inlineStr"/>
       <c r="S14" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-13 ⊂ E-TEC 簽約師傅價值線</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T14" s="5" t="inlineStr">
+      <c r="U14" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 3, "passed": 0, "skipped": 0, "total": 3}</t>
         </is>
@@ -2099,10 +2182,15 @@
       <c r="R15" s="6" t="inlineStr"/>
       <c r="S15" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-14 ⊂ E-TEC 簽約師傅價值線</t>
+        </is>
+      </c>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T15" s="5" t="inlineStr">
+      <c r="U15" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
         </is>
@@ -2177,10 +2265,15 @@
       <c r="R16" s="6" t="inlineStr"/>
       <c r="S16" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-15 ⊂ E-KNW 知識治理價值線</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T16" s="5" t="inlineStr">
+      <c r="U16" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
         </is>
@@ -2255,10 +2348,15 @@
       <c r="R17" s="6" t="inlineStr"/>
       <c r="S17" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-16 ⊂ E-KNW 知識治理價值線</t>
+        </is>
+      </c>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr">
+      <c r="U17" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 3, "passed": 0, "skipped": 0, "total": 3}</t>
         </is>
@@ -2333,10 +2431,15 @@
       <c r="R18" s="6" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-17 ⊂ E-PLT 平台治理價值線</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T18" s="5" t="inlineStr">
+      <c r="U18" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
         </is>
@@ -2411,10 +2514,15 @@
       <c r="R19" s="6" t="inlineStr"/>
       <c r="S19" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-18 ⊂ E-PLT 平台治理價值線</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T19" s="5" t="inlineStr">
+      <c r="U19" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 6, "passed": 0, "skipped": 0, "total": 6}</t>
         </is>
@@ -2489,17 +2597,22 @@
       <c r="R20" s="6" t="inlineStr"/>
       <c r="S20" s="5" t="inlineStr">
         <is>
+          <t>Feature SC-19 ⊂ E-PLT 平台治理價值線</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="T20" s="5" t="inlineStr">
+      <c r="U20" s="5" t="inlineStr">
         <is>
           <t>active {"blocked": 0, "failed": 0, "open": 7, "passed": 0, "skipped": 0, "total": 7}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20"/>
+  <autoFilter ref="A1:U20"/>
   <dataValidations count="1">
     <dataValidation sqref="O2:O20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="只能填四種驗收狀態之一" type="list">
       <formula1>"Not Accepted,Verified,Accepted,Deferred"</formula1>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
@@ -693,36 +693,36 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  驗收契約</t>
+          <t xml:space="preserve">  TC＝驗的單位</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Plane 的 Test Case。守則把 FR／驗收條件／BDD／測試案例壓成「同一個物件」——案例就是驗收條件，省掉一整層追蹤。所以本書講「案例」與講「契約」是同一件事。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+          <t>Plane 的 Test Case。守則把 FR／驗收條件／BDD／測試案例壓成「同一個物件」——一列一個測試案例，回答 FR／NFR 的單一性質『對不對』。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  驗收腳本 ＝ 一條旅程一條</t>
+          <t xml:space="preserve">  SC＝簽核的單位</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>本欄就是這條 SC 在 Plane 的 Test Run（19 條 SC＝19 條 run），內容是該 SC 宣告的那批案例。建立 run 時把每張案例釘在當時的版本，所以舊紀錄不會被日後改版影響。</t>
+          <t>一列一條服務旅程；在驗收執行映射上，每條 SC 各有一個 Plane Test Run（19 條 SC＝19 條 run），內容是該 SC 獨立宣告的 TC 集合，回答整條旅程『順不順』。建立 run 時把每張案例釘在當時的版本，所以舊紀錄不會被日後改版影響。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  括號裡的 UAT-01…UAT-09</t>
+          <t xml:space="preserve">  UAT＝執行的單位</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>22_UAT_Report §4 的走查腳本編號，是「旅程的上層分組」：一支走查涵蓋 1–4 條旅程（UAT-01 撐 SC-01/02/03、UAT-02 撐 SC-04–07）。它回答「這次 UAT 要走哪條路線」，而旅程回答「路線裡的這一段」。⚠️ 它在 Plane 沒有對應物件，只被寫進 run 名稱當註記。</t>
+          <t>22_UAT_Report §4 的 UAT-01…UAT-09 是走查路線：一支走查分組 1–4 條 SC（UAT-01＝SC-01/02/03、UAT-02＝SC-04–07）。它不是 SC 的父層，也不產生另一個簽核狀態；它只回答『UAT 當天走哪條路線』。Plane 沒有對應物件，只寫進 Test Run 名稱當註記。</t>
         </is>
       </c>
     </row>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 旅程驗收主表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 旅程展開（SC × 需求）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 旅程 × Persona（誰在走）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ BDD 行為情境（生成）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="② 旅程驗收主表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="③ 旅程展開（SC × 需求）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="④ 旅程 × Persona（誰在走）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="⑤ BDD 行為情境（生成）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 旅程驗收主表'!$A$1:$U$20</definedName>

--- a/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
+++ b/smartlock-docs/enterprise/規格統控整理/SmartLock_業務邏輯驗收控制表.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="② 旅程驗收主表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="③ 旅程展開（SC × 需求）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="④ 旅程 × Persona（誰在走）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="⑤ BDD 行為情境（生成）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 怎麼用這本" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 旅程驗收主表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 旅程展開（SC × 需求）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ 旅程 × Persona（誰在走）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ BDD 行為情境（生成）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'② 旅程驗收主表'!$A$1:$U$20</definedName>
@@ -1103,7 +1103,7 @@
       <c r="R2" s="6" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-01 ⊂ E-CUS 終端客戶價值線</t>
+          <t>CAP-CONV 智慧客服對話、CAP-MODEL 模型與 AI 治理</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
@@ -1186,7 +1186,7 @@
       <c r="R3" s="6" t="inlineStr"/>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-02 ⊂ E-CUS 終端客戶價值線</t>
+          <t>CAP-CASE 報修建卡、CAP-CONV 智慧客服對話</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
@@ -1269,7 +1269,7 @@
       <c r="R4" s="6" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-03 ⊂ E-CUS 終端客戶價值線</t>
+          <t>CAP-CASE 報修建卡、CAP-CONV 智慧客服對話、CAP-DISP 派工媒合、CAP-EXCEPT 例外治理與稽核</t>
         </is>
       </c>
       <c r="T4" s="5" t="inlineStr">
@@ -1352,7 +1352,7 @@
       <c r="R5" s="6" t="inlineStr"/>
       <c r="S5" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-04 ⊂ E-CUS 終端客戶價值線</t>
+          <t>CAP-DISP 派工媒合、CAP-QUOTE 報價與計費、CAP-WORKBENCH 營運與客戶介面</t>
         </is>
       </c>
       <c r="T5" s="5" t="inlineStr">
@@ -1435,7 +1435,7 @@
       <c r="R6" s="6" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-05 ⊂ E-CUS 終端客戶價值線</t>
+          <t>CAP-DISP 派工媒合</t>
         </is>
       </c>
       <c r="T6" s="5" t="inlineStr">
@@ -1518,7 +1518,7 @@
       <c r="R7" s="6" t="inlineStr"/>
       <c r="S7" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-06 ⊂ E-CUS 終端客戶價值線</t>
+          <t>CAP-DISP 派工媒合、CAP-FIELD 現場作業與結案、CAP-MODEL 模型與 AI 治理</t>
         </is>
       </c>
       <c r="T7" s="5" t="inlineStr">
@@ -1601,7 +1601,7 @@
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-07 ⊂ E-CUS 終端客戶價值線</t>
+          <t>CAP-FIELD 現場作業與結案、CAP-QUOTE 報價與計費</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
@@ -1684,7 +1684,7 @@
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-08 ⊂ E-CUS 終端客戶價值線</t>
+          <t>CAP-EXCEPT 例外治理與稽核、CAP-MONEY 收付與結算</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
@@ -1767,7 +1767,7 @@
       <c r="R10" s="6" t="inlineStr"/>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-09 ⊂ E-CUS 終端客戶價值線</t>
+          <t>CAP-MONEY 收付與結算</t>
         </is>
       </c>
       <c r="T10" s="5" t="inlineStr">
@@ -1850,7 +1850,7 @@
       <c r="R11" s="6" t="inlineStr"/>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-10 ⊂ E-OPS 品牌營運價值線</t>
+          <t>CAP-CASE 報修建卡、CAP-CONV 智慧客服對話、CAP-WORKBENCH 營運與客戶介面</t>
         </is>
       </c>
       <c r="T11" s="5" t="inlineStr">
@@ -1933,7 +1933,7 @@
       <c r="R12" s="6" t="inlineStr"/>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-11 ⊂ E-OPS 品牌營運價值線</t>
+          <t>CAP-EXCEPT 例外治理與稽核、CAP-IAM 身分與權限</t>
         </is>
       </c>
       <c r="T12" s="5" t="inlineStr">
@@ -2016,7 +2016,7 @@
       <c r="R13" s="6" t="inlineStr"/>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-12 ⊂ E-TEC 簽約師傅價值線</t>
+          <t>CAP-IAM 身分與權限、CAP-TECHID 技師身分與准入、CAP-TENANT 租戶開通與治理</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr">
@@ -2099,7 +2099,7 @@
       <c r="R14" s="6" t="inlineStr"/>
       <c r="S14" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-13 ⊂ E-TEC 簽約師傅價值線</t>
+          <t>CAP-MONEY 收付與結算</t>
         </is>
       </c>
       <c r="T14" s="5" t="inlineStr">
@@ -2182,7 +2182,7 @@
       <c r="R15" s="6" t="inlineStr"/>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-14 ⊂ E-TEC 簽約師傅價值線</t>
+          <t>CAP-DISP 派工媒合、CAP-FIELD 現場作業與結案、CAP-TECHID 技師身分與准入</t>
         </is>
       </c>
       <c r="T15" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       <c r="R16" s="6" t="inlineStr"/>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-15 ⊂ E-KNW 知識治理價值線</t>
+          <t>CAP-DATA 資料基座、CAP-KNWLC 知識生命週期</t>
         </is>
       </c>
       <c r="T16" s="5" t="inlineStr">
@@ -2348,7 +2348,7 @@
       <c r="R17" s="6" t="inlineStr"/>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-16 ⊂ E-KNW 知識治理價值線</t>
+          <t>CAP-KNWLC 知識生命週期</t>
         </is>
       </c>
       <c r="T17" s="5" t="inlineStr">
@@ -2431,7 +2431,7 @@
       <c r="R18" s="6" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-17 ⊂ E-PLT 平台治理價值線</t>
+          <t>CAP-DATA 資料基座、CAP-IAM 身分與權限、CAP-TENANT 租戶開通與治理</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       <c r="R19" s="6" t="inlineStr"/>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-18 ⊂ E-PLT 平台治理價值線</t>
+          <t>CAP-IAM 身分與權限、CAP-MODEL 模型與 AI 治理、CAP-TENANT 租戶開通與治理</t>
         </is>
       </c>
       <c r="T19" s="5" t="inlineStr">
@@ -2597,7 +2597,7 @@
       <c r="R20" s="6" t="inlineStr"/>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>Feature SC-19 ⊂ E-PLT 平台治理價值線</t>
+          <t>CAP-EVENT 事件與即時骨幹、CAP-IAM 身分與權限、CAP-PRIV 隱私與資料主體權利</t>
         </is>
       </c>
       <c r="T20" s="5" t="inlineStr">
